--- a/input/timetable/Клиническая психология_.xlsx
+++ b/input/timetable/Клиническая психология_.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="155">
   <si>
     <t>пара</t>
   </si>
@@ -484,9 +484,6 @@
     <t>ФТД: Интернет-консультирование и телефон доверия (лек), Г305</t>
   </si>
   <si>
-    <t>ФТД: Интернет-консультирование и телефон доверия (пр), ЭОиДОТ//</t>
-  </si>
-  <si>
     <t>Общепсихологический практикум, п/г 1, Г106</t>
   </si>
   <si>
@@ -533,6 +530,15 @@
   </si>
   <si>
     <t>Диалогический подход к анализу психотерапевтического процесса (пр), Г319</t>
+  </si>
+  <si>
+    <t>ФТД: Интернет-консультирование и телефон доверия (пр), Г305//</t>
+  </si>
+  <si>
+    <t>Спецпрактикум по продуктивным видам деятельности в практике коррекционно-развивающего обучения (пр), Г317</t>
+  </si>
+  <si>
+    <t>Спецпрактикум по прод.видам деят. в практике коррекционно-развивающего обучения, п/г 1, Г317</t>
   </si>
 </sst>
 </file>
@@ -2133,18 +2139,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2157,10 +2151,37 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2171,21 +2192,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2635,7 +2641,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="112" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D12" s="113"/>
       <c r="E12" s="113"/>
@@ -2647,7 +2653,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="99" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D13" s="100"/>
       <c r="E13" s="100"/>
@@ -2659,7 +2665,7 @@
         <v>4</v>
       </c>
       <c r="C14" s="102" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D14" s="83"/>
       <c r="E14" s="129"/>
@@ -2671,7 +2677,7 @@
         <v>5</v>
       </c>
       <c r="C15" s="103" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D15" s="104"/>
       <c r="E15" s="131"/>
@@ -2685,7 +2691,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="106" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D16" s="107"/>
       <c r="E16" s="107"/>
@@ -2701,7 +2707,7 @@
       </c>
       <c r="D17" s="83"/>
       <c r="E17" s="83" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F17" s="84"/>
     </row>
@@ -2711,7 +2717,7 @@
         <v>3</v>
       </c>
       <c r="C18" s="85" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D18" s="86"/>
       <c r="E18" s="87" t="s">
@@ -2783,7 +2789,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="106" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D24" s="107"/>
       <c r="E24" s="107"/>
@@ -2795,7 +2801,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="93" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D25" s="94"/>
       <c r="E25" s="94"/>
@@ -2807,7 +2813,7 @@
         <v>3</v>
       </c>
       <c r="C26" s="93" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D26" s="94"/>
       <c r="E26" s="94"/>
@@ -2819,7 +2825,7 @@
         <v>4</v>
       </c>
       <c r="C27" s="96" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D27" s="97"/>
       <c r="E27" s="97"/>
@@ -4713,7 +4719,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -4879,7 +4885,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="303" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D14" s="304"/>
       <c r="E14" s="304"/>
@@ -4888,7 +4894,7 @@
     <row r="15" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="26"/>
       <c r="B15" s="57"/>
-      <c r="C15" s="310"/>
+      <c r="C15" s="306"/>
       <c r="D15" s="165"/>
       <c r="E15" s="165"/>
       <c r="F15" s="166"/>
@@ -4900,12 +4906,12 @@
       <c r="B16" s="23">
         <v>1</v>
       </c>
-      <c r="C16" s="311" t="s">
+      <c r="C16" s="307" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="312"/>
-      <c r="E16" s="312"/>
-      <c r="F16" s="313"/>
+      <c r="D16" s="308"/>
+      <c r="E16" s="308"/>
+      <c r="F16" s="309"/>
     </row>
     <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="24"/>
@@ -4936,12 +4942,12 @@
       <c r="B19" s="27">
         <v>8</v>
       </c>
-      <c r="C19" s="319" t="s">
+      <c r="C19" s="314" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="320"/>
-      <c r="E19" s="320"/>
-      <c r="F19" s="321"/>
+      <c r="D19" s="315"/>
+      <c r="E19" s="315"/>
+      <c r="F19" s="316"/>
     </row>
     <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="22" t="s">
@@ -4950,10 +4956,10 @@
       <c r="B20" s="23">
         <v>2</v>
       </c>
-      <c r="C20" s="316"/>
-      <c r="D20" s="317"/>
-      <c r="E20" s="317"/>
-      <c r="F20" s="318"/>
+      <c r="C20" s="321"/>
+      <c r="D20" s="322"/>
+      <c r="E20" s="322"/>
+      <c r="F20" s="323"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="24"/>
@@ -4980,16 +4986,16 @@
       <c r="F22" s="84"/>
     </row>
     <row r="23" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="28"/>
-      <c r="B23" s="27">
-        <v>6</v>
-      </c>
-      <c r="C23" s="319" t="s">
-        <v>136</v>
-      </c>
-      <c r="D23" s="320"/>
-      <c r="E23" s="320"/>
-      <c r="F23" s="321"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="30">
+        <v>5</v>
+      </c>
+      <c r="C23" s="317" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23" s="318"/>
+      <c r="E23" s="318"/>
+      <c r="F23" s="319"/>
     </row>
     <row r="24" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="22" t="s">
@@ -4998,22 +5004,22 @@
       <c r="B24" s="23">
         <v>2</v>
       </c>
-      <c r="C24" s="242" t="s">
+      <c r="C24" s="81" t="s">
+        <v>148</v>
+      </c>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81" t="s">
         <v>149</v>
       </c>
-      <c r="D24" s="322"/>
-      <c r="E24" s="323" t="s">
-        <v>150</v>
-      </c>
-      <c r="F24" s="244"/>
+      <c r="F24" s="82"/>
     </row>
     <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="24"/>
       <c r="B25" s="25">
         <v>3</v>
       </c>
-      <c r="C25" s="102" t="s">
-        <v>152</v>
+      <c r="C25" s="83" t="s">
+        <v>151</v>
       </c>
       <c r="D25" s="83"/>
       <c r="E25" s="83"/>
@@ -5022,182 +5028,208 @@
     <row r="26" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="29"/>
       <c r="B26" s="30">
-        <v>6</v>
-      </c>
-      <c r="C26" s="79"/>
-      <c r="D26" s="314"/>
-      <c r="E26" s="315" t="s">
-        <v>65</v>
-      </c>
-      <c r="F26" s="117"/>
-    </row>
-    <row r="27" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>4</v>
+      </c>
+      <c r="C26" s="83" t="s">
+        <v>153</v>
+      </c>
+      <c r="D26" s="83"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="84"/>
+    </row>
+    <row r="27" spans="1:6" ht="56.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="29"/>
       <c r="B27" s="30">
-        <v>7</v>
-      </c>
-      <c r="C27" s="79"/>
-      <c r="D27" s="314"/>
-      <c r="E27" s="315" t="s">
-        <v>65</v>
-      </c>
-      <c r="F27" s="117"/>
-    </row>
-    <row r="28" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+      <c r="C27" s="83" t="s">
+        <v>154</v>
+      </c>
+      <c r="D27" s="83"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="84"/>
+    </row>
+    <row r="28" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="29"/>
       <c r="B28" s="30">
+        <v>6</v>
+      </c>
+      <c r="C28" s="129"/>
+      <c r="D28" s="129"/>
+      <c r="E28" s="83" t="s">
+        <v>65</v>
+      </c>
+      <c r="F28" s="84"/>
+    </row>
+    <row r="29" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="29"/>
+      <c r="B29" s="30">
+        <v>7</v>
+      </c>
+      <c r="C29" s="129"/>
+      <c r="D29" s="129"/>
+      <c r="E29" s="83" t="s">
+        <v>65</v>
+      </c>
+      <c r="F29" s="84"/>
+    </row>
+    <row r="30" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="28"/>
+      <c r="B30" s="27">
         <v>8</v>
       </c>
-      <c r="C28" s="143"/>
-      <c r="D28" s="144"/>
-      <c r="E28" s="315" t="s">
+      <c r="C30" s="320"/>
+      <c r="D30" s="320"/>
+      <c r="E30" s="311" t="s">
         <v>65</v>
       </c>
-      <c r="F28" s="117"/>
-    </row>
-    <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="22" t="s">
+      <c r="F30" s="312"/>
+    </row>
+    <row r="31" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B31" s="34">
         <v>2</v>
       </c>
-      <c r="C29" s="242" t="s">
+      <c r="C31" s="189" t="s">
         <v>131</v>
       </c>
-      <c r="D29" s="243"/>
-      <c r="E29" s="243"/>
-      <c r="F29" s="244"/>
-    </row>
-    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="31"/>
-      <c r="B30" s="25">
+      <c r="D31" s="190"/>
+      <c r="E31" s="190"/>
+      <c r="F31" s="191"/>
+    </row>
+    <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="31"/>
+      <c r="B32" s="25">
         <v>3</v>
       </c>
-      <c r="C30" s="115" t="s">
+      <c r="C32" s="115" t="s">
         <v>132</v>
       </c>
-      <c r="D30" s="116"/>
-      <c r="E30" s="116"/>
-      <c r="F30" s="117"/>
-    </row>
-    <row r="31" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="31"/>
-      <c r="B31" s="25">
+      <c r="D32" s="116"/>
+      <c r="E32" s="116"/>
+      <c r="F32" s="117"/>
+    </row>
+    <row r="33" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="31"/>
+      <c r="B33" s="25">
         <v>4</v>
       </c>
-      <c r="C31" s="115" t="s">
+      <c r="C33" s="115" t="s">
         <v>88</v>
       </c>
-      <c r="D31" s="116"/>
-      <c r="E31" s="116"/>
-      <c r="F31" s="117"/>
-    </row>
-    <row r="32" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="32"/>
-      <c r="B32" s="27">
+      <c r="D33" s="116"/>
+      <c r="E33" s="116"/>
+      <c r="F33" s="117"/>
+    </row>
+    <row r="34" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="32"/>
+      <c r="B34" s="27">
         <v>5</v>
       </c>
-      <c r="C32" s="103" t="s">
-        <v>151</v>
-      </c>
-      <c r="D32" s="104"/>
-      <c r="E32" s="104"/>
-      <c r="F32" s="206"/>
-    </row>
-    <row r="33" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="46" t="s">
+      <c r="C34" s="103" t="s">
+        <v>150</v>
+      </c>
+      <c r="D34" s="104"/>
+      <c r="E34" s="104"/>
+      <c r="F34" s="206"/>
+    </row>
+    <row r="35" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B35" s="23">
         <v>2</v>
       </c>
-      <c r="C33" s="309" t="s">
+      <c r="C35" s="313" t="s">
         <v>63</v>
       </c>
-      <c r="D33" s="81"/>
-      <c r="E33" s="127"/>
-      <c r="F33" s="128"/>
-    </row>
-    <row r="34" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="40"/>
-      <c r="B34" s="34">
+      <c r="D35" s="81"/>
+      <c r="E35" s="81" t="s">
+        <v>154</v>
+      </c>
+      <c r="F35" s="82"/>
+    </row>
+    <row r="36" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="40"/>
+      <c r="B36" s="34">
         <v>3</v>
       </c>
-      <c r="C34" s="102" t="s">
+      <c r="C36" s="102" t="s">
         <v>63</v>
       </c>
-      <c r="D34" s="83"/>
-      <c r="E34" s="147"/>
-      <c r="F34" s="148"/>
-    </row>
-    <row r="35" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="40"/>
-      <c r="B35" s="34">
+      <c r="D36" s="83"/>
+      <c r="E36" s="147"/>
+      <c r="F36" s="148"/>
+    </row>
+    <row r="37" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="40"/>
+      <c r="B37" s="34">
         <v>4</v>
       </c>
-      <c r="C35" s="102" t="s">
+      <c r="C37" s="102" t="s">
         <v>63</v>
       </c>
-      <c r="D35" s="83"/>
-      <c r="E35" s="147"/>
-      <c r="F35" s="148"/>
-    </row>
-    <row r="36" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="47"/>
-      <c r="B36" s="27">
+      <c r="D37" s="83"/>
+      <c r="E37" s="147"/>
+      <c r="F37" s="148"/>
+    </row>
+    <row r="38" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="47"/>
+      <c r="B38" s="27">
         <v>5</v>
       </c>
-      <c r="C36" s="306" t="s">
+      <c r="C38" s="310" t="s">
         <v>85</v>
       </c>
-      <c r="D36" s="307"/>
-      <c r="E36" s="307"/>
-      <c r="F36" s="308"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B37" s="2" t="s">
+      <c r="D38" s="311"/>
+      <c r="E38" s="311"/>
+      <c r="F38" s="312"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B38" s="2" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B40" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C27:D27"/>
+  <mergeCells count="38">
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C21:F21"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
     <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C31:F31"/>
     <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C33:F33"/>
     <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
     <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="C17:F17"/>
@@ -5208,6 +5240,9 @@
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
   </mergeCells>
   <conditionalFormatting sqref="C9">
     <cfRule type="expression" priority="1">

--- a/input/timetable/Клиническая психология_.xlsx
+++ b/input/timetable/Клиническая психология_.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="195">
   <si>
     <t>пара</t>
   </si>
@@ -78,6 +78,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>гуманитарного образования и спорта</t>
   </si>
   <si>
@@ -126,9 +129,39 @@
     <t>весенний</t>
   </si>
   <si>
+    <t>Плеханова Н.П.</t>
+  </si>
+  <si>
+    <t>Усаева Н.Р.</t>
+  </si>
+  <si>
+    <t>Грехова И.П.</t>
+  </si>
+  <si>
+    <t>Давыдова А.М.</t>
+  </si>
+  <si>
+    <t>Шибаева Л.В.</t>
+  </si>
+  <si>
+    <t>Гузич М.Э.</t>
+  </si>
+  <si>
+    <t>Шумилов С.П.</t>
+  </si>
+  <si>
     <t>Русский язык и культура речи (лек 32 ч)</t>
   </si>
   <si>
+    <t>Хадынская А.А.</t>
+  </si>
+  <si>
+    <t>Меренков В.А.</t>
+  </si>
+  <si>
+    <t>Войтович О.Н.</t>
+  </si>
+  <si>
     <t>Философия (лек 32 ч)</t>
   </si>
   <si>
@@ -138,12 +171,36 @@
     <t>Общая психология (лек), Г306</t>
   </si>
   <si>
+    <t>Клочко Н.П.</t>
+  </si>
+  <si>
+    <t>Самойлова М.В.</t>
+  </si>
+  <si>
+    <t>Родермель Т.А.</t>
+  </si>
+  <si>
+    <t>Леденцова С.Л.</t>
+  </si>
+  <si>
+    <t>Бокова Е.В.</t>
+  </si>
+  <si>
     <t>Нейропсихология детского возраста (лек), ЭОиДОТ</t>
   </si>
   <si>
     <t>203-31</t>
   </si>
   <si>
+    <t>Белоус П.В</t>
+  </si>
+  <si>
+    <t>Хохлова Н.И.</t>
+  </si>
+  <si>
+    <t>Дроздова А.А.</t>
+  </si>
+  <si>
     <t>Психология инклюзивного общества (лекция 16 ч)</t>
   </si>
   <si>
@@ -201,6 +258,12 @@
     <t>Акмеология и геронтопсихология (лек), Г305</t>
   </si>
   <si>
+    <t>Кочиева Д.И.</t>
+  </si>
+  <si>
+    <t>Чуранова О.В.</t>
+  </si>
+  <si>
     <t>Возрастная физиология (лек), Г305</t>
   </si>
   <si>
@@ -222,9 +285,15 @@
     <t>Психологическая супервизия, п/г 2, ЭОиДОТ</t>
   </si>
   <si>
+    <t>Шамухаметова Е.С.</t>
+  </si>
+  <si>
     <t>Психосоматика (лек), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Рагозинская В.Г.</t>
+  </si>
+  <si>
     <t>Психосоматика (пр), ЭОиДОТ</t>
   </si>
   <si>
@@ -235,6 +304,9 @@
   </si>
   <si>
     <t>Диагностика и коррекция аномалий поведения в период  подросткового кризиса, п/г 1, Г318</t>
+  </si>
+  <si>
+    <t>Шелюк О.Н.</t>
   </si>
   <si>
     <t>Начальник УОпоОФО</t>
@@ -316,6 +388,12 @@
     <t>Патопсихологическая диагностика и психотерапия                                                                                                  (ТО: 02.02.2026-30.05.2026)</t>
   </si>
   <si>
+    <t>Афян К.А..;  Шумилов С.П.</t>
+  </si>
+  <si>
+    <t>Кулагина И.В.</t>
+  </si>
+  <si>
     <t>Основы проектной деятельности (лек 16 ч)</t>
   </si>
   <si>
@@ -328,6 +406,9 @@
     <t>Психология невротизации (лек), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Батыршина К.Г.</t>
+  </si>
+  <si>
     <t>Нейропсихология детского возраста (пр), ЭОиДОТ</t>
   </si>
   <si>
@@ -343,6 +424,15 @@
     <t>Диалогический подход к анализу психотерапевтического процесса (лек), Г306</t>
   </si>
   <si>
+    <t>Белоус П.В.</t>
+  </si>
+  <si>
+    <t>Лепихина Ю.В.</t>
+  </si>
+  <si>
+    <t>Шумилов С.П.; Воробьева А.Д.</t>
+  </si>
+  <si>
     <t>Иностранный язык, п/г 2, Г104</t>
   </si>
   <si>
@@ -358,6 +448,9 @@
     <t>Элективные дисциплины по физической культуре и спорту проводятся  1 парой или  2 парой в зависимости от выбранной элективной дисциплины</t>
   </si>
   <si>
+    <t>Плесовских И.Н.</t>
+  </si>
+  <si>
     <t>Психофизиология (пр), Г306</t>
   </si>
   <si>
@@ -367,6 +460,18 @@
     <t>Психология профессионального  самоопределения (пр), Г306</t>
   </si>
   <si>
+    <t>Кулагина И.В./Плесовских И.Н.</t>
+  </si>
+  <si>
+    <t>Орехова Е.Ю</t>
+  </si>
+  <si>
+    <t>Батыршина К.Г.; Бастинович Е.В.</t>
+  </si>
+  <si>
+    <t>Войтович О.Н./Шибаева Л.В.</t>
+  </si>
+  <si>
     <t>Общая психология (пр), Г306//</t>
   </si>
   <si>
@@ -406,12 +511,18 @@
     <t>Методика преподавания в высшей школе (пр). Г317</t>
   </si>
   <si>
+    <t>Хохлова Н.И./Меренков В.А.</t>
+  </si>
+  <si>
     <t>Производственная практика, педагогическая практика, Г304// Психология инклюзивного общества (пр), Г304</t>
   </si>
   <si>
     <t>Возрастная физиология (пр), Г305</t>
   </si>
   <si>
+    <t>Батыршина К.Г.; Шелюк О.Н.</t>
+  </si>
+  <si>
     <t>Практикум по патопсихологии, п/г 2, Г304</t>
   </si>
   <si>
@@ -532,6 +643,12 @@
     <t>Диалогический подход к анализу психотерапевтического процесса (пр), Г319</t>
   </si>
   <si>
+    <t>вакансия</t>
+  </si>
+  <si>
+    <t>Шелюк О.Н.;вакансия</t>
+  </si>
+  <si>
     <t>ФТД: Интернет-консультирование и телефон доверия (пр), Г305//</t>
   </si>
   <si>
@@ -539,6 +656,9 @@
   </si>
   <si>
     <t>Спецпрактикум по прод.видам деят. в практике коррекционно-развивающего обучения, п/г 1, Г317</t>
+  </si>
+  <si>
+    <t>Клочко Н.П.;Меренков В.А.</t>
   </si>
 </sst>
 </file>
@@ -664,7 +784,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -683,6 +803,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -694,7 +820,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="57">
+  <borders count="59">
     <border>
       <left/>
       <right/>
@@ -839,6 +965,19 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1286,6 +1425,17 @@
     </border>
     <border>
       <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -1412,7 +1562,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="324">
+  <cellXfs count="351">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1451,16 +1601,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1469,6 +1616,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1490,10 +1643,10 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1502,16 +1655,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1520,29 +1673,32 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1557,26 +1713,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1585,60 +1742,134 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1648,49 +1879,49 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1699,83 +1930,53 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1783,145 +1984,184 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1930,129 +2170,83 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2062,76 +2256,92 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -2139,59 +2349,32 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2501,7 +2684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2510,10 +2693,11 @@
     <col min="4" max="4" width="18.85546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="19" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.85546875" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2521,15 +2705,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -2537,13 +2721,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -2553,29 +2737,29 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="52" t="s">
+    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="92" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="92"/>
+      <c r="C7" s="149" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="149"/>
       <c r="E7" s="10">
         <v>1</v>
       </c>
@@ -2583,35 +2767,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="84" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="14" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="105" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="105"/>
-      <c r="E9" s="105"/>
-      <c r="F9" s="105"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="163" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="163"/>
+      <c r="E9" s="163"/>
+      <c r="F9" s="163"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>0</v>
@@ -2622,352 +2806,426 @@
       <c r="D10" s="19"/>
       <c r="E10" s="20"/>
       <c r="F10" s="21"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="23">
+      <c r="G10" s="22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="24">
         <v>1</v>
       </c>
-      <c r="C11" s="109"/>
-      <c r="D11" s="110"/>
-      <c r="E11" s="110"/>
-      <c r="F11" s="111"/>
-    </row>
-    <row r="12" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25">
+      <c r="C11" s="164"/>
+      <c r="D11" s="165"/>
+      <c r="E11" s="165"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="64"/>
+    </row>
+    <row r="12" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26">
         <v>2</v>
       </c>
-      <c r="C12" s="112" t="s">
-        <v>142</v>
-      </c>
-      <c r="D12" s="113"/>
-      <c r="E12" s="113"/>
-      <c r="F12" s="114"/>
-    </row>
-    <row r="13" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25">
+      <c r="C12" s="167" t="s">
+        <v>179</v>
+      </c>
+      <c r="D12" s="168"/>
+      <c r="E12" s="168"/>
+      <c r="F12" s="169"/>
+      <c r="G12" s="85" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26">
         <v>3</v>
       </c>
-      <c r="C13" s="99" t="s">
-        <v>143</v>
-      </c>
-      <c r="D13" s="100"/>
-      <c r="E13" s="100"/>
-      <c r="F13" s="101"/>
-    </row>
-    <row r="14" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="24"/>
-      <c r="B14" s="25">
+      <c r="C13" s="156" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="157"/>
+      <c r="E13" s="157"/>
+      <c r="F13" s="158"/>
+      <c r="G13" s="85" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="25"/>
+      <c r="B14" s="26">
         <v>4</v>
       </c>
-      <c r="C14" s="102" t="s">
-        <v>136</v>
-      </c>
-      <c r="D14" s="83"/>
-      <c r="E14" s="129"/>
-      <c r="F14" s="130"/>
-    </row>
-    <row r="15" spans="1:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27">
+      <c r="C14" s="159" t="s">
+        <v>173</v>
+      </c>
+      <c r="D14" s="160"/>
+      <c r="E14" s="115"/>
+      <c r="F14" s="116"/>
+      <c r="G14" s="85" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="27"/>
+      <c r="B15" s="28">
         <v>5</v>
       </c>
-      <c r="C15" s="103" t="s">
-        <v>137</v>
-      </c>
-      <c r="D15" s="104"/>
-      <c r="E15" s="131"/>
-      <c r="F15" s="132"/>
-    </row>
-    <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="56">
+      <c r="C15" s="161" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" s="162"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="118"/>
+      <c r="G15" s="87" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="60">
         <v>1</v>
       </c>
-      <c r="C16" s="106" t="s">
-        <v>139</v>
-      </c>
-      <c r="D16" s="107"/>
-      <c r="E16" s="107"/>
-      <c r="F16" s="108"/>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25">
+      <c r="C16" s="140" t="s">
+        <v>176</v>
+      </c>
+      <c r="D16" s="141"/>
+      <c r="E16" s="141"/>
+      <c r="F16" s="142"/>
+      <c r="G16" s="99" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="25"/>
+      <c r="B17" s="26">
         <v>2</v>
       </c>
-      <c r="C17" s="102" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83" t="s">
-        <v>140</v>
-      </c>
-      <c r="F17" s="84"/>
-    </row>
-    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="24"/>
-      <c r="B18" s="25">
+      <c r="C17" s="159" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="160"/>
+      <c r="E17" s="160" t="s">
+        <v>177</v>
+      </c>
+      <c r="F17" s="170"/>
+      <c r="G17" s="85" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="25"/>
+      <c r="B18" s="26">
         <v>3</v>
       </c>
-      <c r="C18" s="85" t="s">
-        <v>138</v>
-      </c>
-      <c r="D18" s="86"/>
-      <c r="E18" s="87" t="s">
-        <v>89</v>
-      </c>
-      <c r="F18" s="88"/>
-    </row>
-    <row r="19" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="28"/>
-      <c r="B19" s="57">
+      <c r="C18" s="178" t="s">
+        <v>175</v>
+      </c>
+      <c r="D18" s="179"/>
+      <c r="E18" s="180" t="s">
+        <v>119</v>
+      </c>
+      <c r="F18" s="181"/>
+      <c r="G18" s="85" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="29"/>
+      <c r="B19" s="61">
         <v>4</v>
       </c>
-      <c r="C19" s="143"/>
-      <c r="D19" s="144"/>
-      <c r="E19" s="144"/>
-      <c r="F19" s="145"/>
-    </row>
-    <row r="20" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="23">
+      <c r="C19" s="131"/>
+      <c r="D19" s="132"/>
+      <c r="E19" s="132"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="81"/>
+    </row>
+    <row r="20" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="24">
         <v>1</v>
       </c>
-      <c r="C20" s="118"/>
-      <c r="D20" s="119"/>
-      <c r="E20" s="81" t="s">
-        <v>90</v>
-      </c>
-      <c r="F20" s="82"/>
-    </row>
-    <row r="21" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25">
+      <c r="C20" s="174"/>
+      <c r="D20" s="175"/>
+      <c r="E20" s="176" t="s">
+        <v>120</v>
+      </c>
+      <c r="F20" s="177"/>
+      <c r="G20" s="99" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="25"/>
+      <c r="B21" s="26">
         <v>2</v>
       </c>
-      <c r="C21" s="79"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="83" t="s">
-        <v>91</v>
-      </c>
-      <c r="F21" s="84"/>
-    </row>
-    <row r="22" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="24"/>
-      <c r="B22" s="25">
+      <c r="C21" s="128"/>
+      <c r="D21" s="129"/>
+      <c r="E21" s="160" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" s="170"/>
+      <c r="G21" s="85" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="25"/>
+      <c r="B22" s="26">
         <v>3</v>
       </c>
-      <c r="C22" s="115" t="s">
+      <c r="C22" s="171" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="172"/>
+      <c r="E22" s="172"/>
+      <c r="F22" s="173"/>
+      <c r="G22" s="85" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="29"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="119"/>
+      <c r="D23" s="120"/>
+      <c r="E23" s="120"/>
+      <c r="F23" s="121"/>
+      <c r="G23" s="81"/>
+    </row>
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="24">
+        <v>1</v>
+      </c>
+      <c r="C24" s="140" t="s">
+        <v>178</v>
+      </c>
+      <c r="D24" s="141"/>
+      <c r="E24" s="141"/>
+      <c r="F24" s="142"/>
+      <c r="G24" s="86" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="25"/>
+      <c r="B25" s="26">
+        <v>2</v>
+      </c>
+      <c r="C25" s="150" t="s">
+        <v>181</v>
+      </c>
+      <c r="D25" s="151"/>
+      <c r="E25" s="151"/>
+      <c r="F25" s="152"/>
+      <c r="G25" s="85" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="30"/>
+      <c r="B26" s="31">
+        <v>3</v>
+      </c>
+      <c r="C26" s="150" t="s">
+        <v>182</v>
+      </c>
+      <c r="D26" s="151"/>
+      <c r="E26" s="151"/>
+      <c r="F26" s="152"/>
+      <c r="G26" s="85" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="29"/>
+      <c r="B27" s="28">
+        <v>4</v>
+      </c>
+      <c r="C27" s="153" t="s">
+        <v>183</v>
+      </c>
+      <c r="D27" s="154"/>
+      <c r="E27" s="154"/>
+      <c r="F27" s="155"/>
+      <c r="G27" s="87" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="24">
+        <v>1</v>
+      </c>
+      <c r="C28" s="146"/>
+      <c r="D28" s="147"/>
+      <c r="E28" s="147"/>
+      <c r="F28" s="148"/>
+      <c r="G28" s="86"/>
+    </row>
+    <row r="29" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="32"/>
+      <c r="B29" s="26">
+        <v>2</v>
+      </c>
+      <c r="C29" s="106" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="107"/>
+      <c r="E29" s="107"/>
+      <c r="F29" s="108"/>
+      <c r="G29" s="88" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="32"/>
+      <c r="B30" s="59">
+        <v>3</v>
+      </c>
+      <c r="C30" s="106" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30" s="107"/>
+      <c r="E30" s="107"/>
+      <c r="F30" s="108"/>
+      <c r="G30" s="88" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="33"/>
+      <c r="B31" s="28">
+        <v>4</v>
+      </c>
+      <c r="C31" s="143"/>
+      <c r="D31" s="144"/>
+      <c r="E31" s="144"/>
+      <c r="F31" s="145"/>
+      <c r="G31" s="81"/>
+    </row>
+    <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="D22" s="116"/>
-      <c r="E22" s="116"/>
-      <c r="F22" s="117"/>
-    </row>
-    <row r="23" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="28"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="133"/>
-      <c r="D23" s="134"/>
-      <c r="E23" s="134"/>
-      <c r="F23" s="135"/>
-    </row>
-    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="23">
+      <c r="B32" s="35">
         <v>1</v>
       </c>
-      <c r="C24" s="106" t="s">
-        <v>141</v>
-      </c>
-      <c r="D24" s="107"/>
-      <c r="E24" s="107"/>
-      <c r="F24" s="108"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25">
+      <c r="C32" s="125"/>
+      <c r="D32" s="126"/>
+      <c r="E32" s="126"/>
+      <c r="F32" s="127"/>
+      <c r="G32" s="79"/>
+    </row>
+    <row r="33" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="32"/>
+      <c r="B33" s="36">
         <v>2</v>
       </c>
-      <c r="C25" s="93" t="s">
-        <v>144</v>
-      </c>
-      <c r="D25" s="94"/>
-      <c r="E25" s="94"/>
-      <c r="F25" s="95"/>
-    </row>
-    <row r="26" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="29"/>
-      <c r="B26" s="30">
+      <c r="C33" s="128"/>
+      <c r="D33" s="129"/>
+      <c r="E33" s="129"/>
+      <c r="F33" s="130"/>
+      <c r="G33" s="79"/>
+    </row>
+    <row r="34" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="37"/>
+      <c r="B34" s="31">
         <v>3</v>
       </c>
-      <c r="C26" s="93" t="s">
-        <v>145</v>
-      </c>
-      <c r="D26" s="94"/>
-      <c r="E26" s="94"/>
-      <c r="F26" s="95"/>
-    </row>
-    <row r="27" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="28"/>
-      <c r="B27" s="27">
-        <v>4</v>
-      </c>
-      <c r="C27" s="96" t="s">
-        <v>146</v>
-      </c>
-      <c r="D27" s="97"/>
-      <c r="E27" s="97"/>
-      <c r="F27" s="98"/>
-    </row>
-    <row r="28" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="23">
-        <v>1</v>
-      </c>
-      <c r="C28" s="89"/>
-      <c r="D28" s="90"/>
-      <c r="E28" s="90"/>
-      <c r="F28" s="91"/>
-    </row>
-    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="31"/>
-      <c r="B29" s="25">
-        <v>2</v>
-      </c>
-      <c r="C29" s="120" t="s">
-        <v>51</v>
-      </c>
-      <c r="D29" s="121"/>
-      <c r="E29" s="121"/>
-      <c r="F29" s="122"/>
-    </row>
-    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="31"/>
-      <c r="B30" s="55">
-        <v>3</v>
-      </c>
-      <c r="C30" s="120" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30" s="121"/>
-      <c r="E30" s="121"/>
-      <c r="F30" s="122"/>
-    </row>
-    <row r="31" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="32"/>
-      <c r="B31" s="27">
-        <v>4</v>
-      </c>
-      <c r="C31" s="152"/>
-      <c r="D31" s="153"/>
-      <c r="E31" s="153"/>
-      <c r="F31" s="154"/>
-    </row>
-    <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="B32" s="34">
-        <v>1</v>
-      </c>
-      <c r="C32" s="139"/>
-      <c r="D32" s="140"/>
-      <c r="E32" s="140"/>
-      <c r="F32" s="141"/>
-    </row>
-    <row r="33" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="31"/>
-      <c r="B33" s="35">
-        <v>2</v>
-      </c>
-      <c r="C33" s="79"/>
-      <c r="D33" s="80"/>
-      <c r="E33" s="80"/>
-      <c r="F33" s="142"/>
-    </row>
-    <row r="34" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="36"/>
-      <c r="B34" s="30">
-        <v>3</v>
-      </c>
-      <c r="C34" s="123" t="s">
-        <v>29</v>
-      </c>
-      <c r="D34" s="124"/>
-      <c r="E34" s="124"/>
-      <c r="F34" s="125"/>
-    </row>
-    <row r="35" spans="1:6" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="37"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="149"/>
-      <c r="D35" s="150"/>
-      <c r="E35" s="150"/>
-      <c r="F35" s="151"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="62"/>
-      <c r="B36" s="66" t="s">
+      <c r="C34" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" s="110"/>
+      <c r="E34" s="110"/>
+      <c r="F34" s="111"/>
+      <c r="G34" s="85" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="38"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="137"/>
+      <c r="D35" s="138"/>
+      <c r="E35" s="138"/>
+      <c r="F35" s="139"/>
+      <c r="G35" s="100"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="67"/>
+      <c r="B36" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="112" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" s="113"/>
+      <c r="E36" s="113"/>
+      <c r="F36" s="114"/>
+      <c r="G36" s="94" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="68"/>
+      <c r="B37" s="72" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="134" t="s">
+        <v>69</v>
+      </c>
+      <c r="D37" s="135"/>
+      <c r="E37" s="135"/>
+      <c r="F37" s="136"/>
+      <c r="G37" s="85" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" s="69"/>
+      <c r="B38" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" s="123"/>
+      <c r="E38" s="123"/>
+      <c r="F38" s="124"/>
+      <c r="G38" s="92" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="70"/>
+      <c r="B39" s="74" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="C36" s="126" t="s">
-        <v>34</v>
-      </c>
-      <c r="D36" s="127"/>
-      <c r="E36" s="127"/>
-      <c r="F36" s="128"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="63"/>
-      <c r="B37" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="C37" s="146" t="s">
-        <v>50</v>
-      </c>
-      <c r="D37" s="147"/>
-      <c r="E37" s="147"/>
-      <c r="F37" s="148"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A38" s="64"/>
-      <c r="B38" s="68" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="136" t="s">
-        <v>49</v>
-      </c>
-      <c r="D38" s="137"/>
-      <c r="E38" s="137"/>
-      <c r="F38" s="138"/>
-    </row>
-    <row r="39" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="65"/>
-      <c r="B39" s="69" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" s="123" t="s">
-        <v>31</v>
-      </c>
-      <c r="D39" s="124"/>
-      <c r="E39" s="124"/>
-      <c r="F39" s="125"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D39" s="110"/>
+      <c r="E39" s="110"/>
+      <c r="F39" s="111"/>
+      <c r="G39" s="98" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B41" s="2" t="s">
         <v>16</v>
       </c>
@@ -2975,7 +3233,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B42" s="2" t="s">
         <v>17</v>
       </c>
@@ -2985,6 +3243,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="C36:F36"/>
@@ -3001,27 +3280,6 @@
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
   </mergeCells>
   <conditionalFormatting sqref="C9">
     <cfRule type="expression" priority="1">
@@ -3044,7 +3302,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3053,10 +3311,11 @@
     <col min="4" max="4" width="19" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -3064,15 +3323,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -3080,13 +3339,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -3096,30 +3355,30 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="52" t="s">
+    <row r="7" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="92" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="92"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="149" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="149"/>
       <c r="E7" s="10">
         <v>2</v>
       </c>
@@ -3127,38 +3386,38 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="84" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="14" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="61" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="60"/>
-      <c r="C9" s="105" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" s="105"/>
-      <c r="E9" s="105"/>
-      <c r="F9" s="105"/>
-    </row>
-    <row r="10" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="43" t="s">
+    <row r="9" spans="1:19" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="44" t="s">
+      <c r="B9" s="65"/>
+      <c r="C9" s="163" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="163"/>
+      <c r="E9" s="163"/>
+      <c r="F9" s="163"/>
+    </row>
+    <row r="10" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="45" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="18" t="s">
@@ -3167,361 +3426,430 @@
       <c r="D10" s="19"/>
       <c r="E10" s="20"/>
       <c r="F10" s="21"/>
-      <c r="Q10" s="54"/>
-      <c r="R10" s="54"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A11" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="200" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="201"/>
-      <c r="E11" s="201"/>
-      <c r="F11" s="202"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25">
+      <c r="G10" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="R10" s="58"/>
+      <c r="S10" s="58"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A11" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="184" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="185"/>
+      <c r="E11" s="185"/>
+      <c r="F11" s="186"/>
+      <c r="G11" s="64"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26">
         <v>4</v>
       </c>
-      <c r="C12" s="120" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" s="121"/>
-      <c r="E12" s="161"/>
-      <c r="F12" s="162"/>
-      <c r="L12" s="58"/>
-    </row>
-    <row r="13" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="29"/>
-      <c r="B13" s="30">
+      <c r="C12" s="106" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" s="107"/>
+      <c r="E12" s="228"/>
+      <c r="F12" s="229"/>
+      <c r="G12" s="85" t="s">
+        <v>129</v>
+      </c>
+      <c r="M12" s="62"/>
+    </row>
+    <row r="13" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="30"/>
+      <c r="B13" s="31">
         <v>5</v>
       </c>
-      <c r="C13" s="120" t="s">
-        <v>99</v>
-      </c>
-      <c r="D13" s="121"/>
-      <c r="E13" s="121" t="s">
-        <v>101</v>
-      </c>
-      <c r="F13" s="122"/>
-      <c r="L13" s="58"/>
-    </row>
-    <row r="14" spans="1:18" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27">
+      <c r="C13" s="106" t="s">
+        <v>134</v>
+      </c>
+      <c r="D13" s="107"/>
+      <c r="E13" s="107" t="s">
+        <v>136</v>
+      </c>
+      <c r="F13" s="108"/>
+      <c r="G13" s="85" t="s">
+        <v>130</v>
+      </c>
+      <c r="M13" s="62"/>
+    </row>
+    <row r="14" spans="1:19" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="27"/>
+      <c r="B14" s="28">
         <v>6</v>
       </c>
-      <c r="C14" s="163" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" s="164"/>
-      <c r="E14" s="165"/>
-      <c r="F14" s="166"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A15" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="23">
+      <c r="C14" s="230" t="s">
+        <v>135</v>
+      </c>
+      <c r="D14" s="231"/>
+      <c r="E14" s="232"/>
+      <c r="F14" s="233"/>
+      <c r="G14" s="98" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A15" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="24">
         <v>1</v>
       </c>
-      <c r="C15" s="203"/>
-      <c r="D15" s="204"/>
-      <c r="E15" s="204"/>
-      <c r="F15" s="205"/>
-    </row>
-    <row r="16" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25">
+      <c r="C15" s="187"/>
+      <c r="D15" s="188"/>
+      <c r="E15" s="188"/>
+      <c r="F15" s="189"/>
+      <c r="G15" s="64"/>
+    </row>
+    <row r="16" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26">
         <v>2</v>
       </c>
-      <c r="C16" s="112" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="113"/>
-      <c r="E16" s="113"/>
-      <c r="F16" s="114"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25">
+      <c r="C16" s="167" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="168"/>
+      <c r="E16" s="168"/>
+      <c r="F16" s="169"/>
+      <c r="G16" s="85" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A17" s="25"/>
+      <c r="B17" s="26">
         <v>3</v>
       </c>
-      <c r="C17" s="112" t="s">
+      <c r="C17" s="167" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="168"/>
+      <c r="E17" s="168"/>
+      <c r="F17" s="169"/>
+      <c r="G17" s="85" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="25"/>
+      <c r="B18" s="26">
+        <v>4</v>
+      </c>
+      <c r="C18" s="159" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="160"/>
+      <c r="E18" s="160"/>
+      <c r="F18" s="170"/>
+      <c r="G18" s="85" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="29"/>
+      <c r="B19" s="28">
+        <v>5</v>
+      </c>
+      <c r="C19" s="161" t="s">
+        <v>127</v>
+      </c>
+      <c r="D19" s="162"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="190"/>
+      <c r="G19" s="85" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="71">
+        <v>1</v>
+      </c>
+      <c r="C20" s="195" t="s">
+        <v>107</v>
+      </c>
+      <c r="D20" s="196"/>
+      <c r="E20" s="196"/>
+      <c r="F20" s="197"/>
+      <c r="G20" s="99" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="103"/>
+      <c r="B21" s="72">
+        <v>2</v>
+      </c>
+      <c r="C21" s="191" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="192"/>
+      <c r="E21" s="192"/>
+      <c r="F21" s="193"/>
+      <c r="G21" s="85" t="s">
+        <v>41</v>
+      </c>
+      <c r="O21" s="78"/>
+    </row>
+    <row r="22" spans="1:15" ht="31.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="103"/>
+      <c r="B22" s="104">
+        <v>3</v>
+      </c>
+      <c r="C22" s="198"/>
+      <c r="D22" s="199"/>
+      <c r="E22" s="200" t="s">
+        <v>121</v>
+      </c>
+      <c r="F22" s="201"/>
+      <c r="G22" s="88" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="103"/>
+      <c r="B23" s="105">
+        <v>4</v>
+      </c>
+      <c r="C23" s="182"/>
+      <c r="D23" s="183"/>
+      <c r="E23" s="107" t="s">
+        <v>137</v>
+      </c>
+      <c r="F23" s="108"/>
+      <c r="G23" s="85" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="202" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="203"/>
+      <c r="E24" s="203"/>
+      <c r="F24" s="204"/>
+      <c r="G24" s="64"/>
+    </row>
+    <row r="25" spans="1:15" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="25"/>
+      <c r="B25" s="26">
+        <v>4</v>
+      </c>
+      <c r="C25" s="191" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="192"/>
+      <c r="E25" s="192"/>
+      <c r="F25" s="193"/>
+      <c r="G25" s="85" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="30"/>
+      <c r="B26" s="31">
+        <v>5</v>
+      </c>
+      <c r="C26" s="191" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" s="192"/>
+      <c r="E26" s="192"/>
+      <c r="F26" s="193"/>
+      <c r="G26" s="92" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="29"/>
+      <c r="B27" s="28">
+        <v>6</v>
+      </c>
+      <c r="C27" s="223" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" s="224"/>
+      <c r="E27" s="224"/>
+      <c r="F27" s="225"/>
+      <c r="G27" s="98" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="24">
+        <v>1</v>
+      </c>
+      <c r="C28" s="164"/>
+      <c r="D28" s="165"/>
+      <c r="E28" s="165"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="64"/>
+    </row>
+    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="32"/>
+      <c r="B29" s="26">
+        <v>2</v>
+      </c>
+      <c r="C29" s="198"/>
+      <c r="D29" s="226"/>
+      <c r="E29" s="226"/>
+      <c r="F29" s="227"/>
+      <c r="G29" s="85"/>
+    </row>
+    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="32"/>
+      <c r="B30" s="26">
+        <v>3</v>
+      </c>
+      <c r="C30" s="106" t="s">
+        <v>139</v>
+      </c>
+      <c r="D30" s="107"/>
+      <c r="E30" s="107"/>
+      <c r="F30" s="108"/>
+      <c r="G30" s="85" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="32"/>
+      <c r="B31" s="26">
+        <v>4</v>
+      </c>
+      <c r="C31" s="159" t="s">
+        <v>140</v>
+      </c>
+      <c r="D31" s="160"/>
+      <c r="E31" s="160"/>
+      <c r="F31" s="170"/>
+      <c r="G31" s="85" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="33"/>
+      <c r="B32" s="28">
+        <v>5</v>
+      </c>
+      <c r="C32" s="220"/>
+      <c r="D32" s="221"/>
+      <c r="E32" s="221"/>
+      <c r="F32" s="222"/>
+      <c r="G32" s="87"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" s="24">
+        <v>2</v>
+      </c>
+      <c r="C33" s="217" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" s="218"/>
+      <c r="E33" s="218"/>
+      <c r="F33" s="219"/>
+      <c r="G33" s="47"/>
+    </row>
+    <row r="34" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="50"/>
+      <c r="B34" s="28">
+        <v>3</v>
+      </c>
+      <c r="C34" s="208"/>
+      <c r="D34" s="209"/>
+      <c r="E34" s="209"/>
+      <c r="F34" s="210"/>
+      <c r="G34" s="48"/>
+    </row>
+    <row r="35" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="51"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="211"/>
+      <c r="D35" s="212"/>
+      <c r="E35" s="212"/>
+      <c r="F35" s="213"/>
+      <c r="G35" s="53"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="40"/>
+      <c r="B36" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="214" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="113"/>
-      <c r="E17" s="113"/>
-      <c r="F17" s="114"/>
-    </row>
-    <row r="18" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="24"/>
-      <c r="B18" s="25">
-        <v>4</v>
-      </c>
-      <c r="C18" s="102" t="s">
-        <v>95</v>
-      </c>
-      <c r="D18" s="83"/>
-      <c r="E18" s="83"/>
-      <c r="F18" s="84"/>
-    </row>
-    <row r="19" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="28"/>
-      <c r="B19" s="27">
-        <v>5</v>
-      </c>
-      <c r="C19" s="103" t="s">
-        <v>96</v>
-      </c>
-      <c r="D19" s="104"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="206"/>
-    </row>
-    <row r="20" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="75" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="66">
-        <v>1</v>
-      </c>
-      <c r="C20" s="168" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" s="169"/>
-      <c r="E20" s="169"/>
-      <c r="F20" s="170"/>
-    </row>
-    <row r="21" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="76"/>
-      <c r="B21" s="67">
-        <v>2</v>
-      </c>
-      <c r="C21" s="155" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="156"/>
-      <c r="E21" s="156"/>
-      <c r="F21" s="157"/>
-      <c r="N21" s="72"/>
-    </row>
-    <row r="22" spans="1:14" ht="31.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="76"/>
-      <c r="B22" s="77">
-        <v>3</v>
-      </c>
-      <c r="C22" s="158"/>
-      <c r="D22" s="171"/>
-      <c r="E22" s="172" t="s">
-        <v>91</v>
-      </c>
-      <c r="F22" s="173"/>
-    </row>
-    <row r="23" spans="1:14" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="76"/>
-      <c r="B23" s="78">
-        <v>4</v>
-      </c>
-      <c r="C23" s="198"/>
-      <c r="D23" s="199"/>
-      <c r="E23" s="121" t="s">
-        <v>102</v>
-      </c>
-      <c r="F23" s="122"/>
-    </row>
-    <row r="24" spans="1:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" s="174" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="175"/>
-      <c r="E24" s="175"/>
-      <c r="F24" s="176"/>
-    </row>
-    <row r="25" spans="1:14" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25">
-        <v>4</v>
-      </c>
-      <c r="C25" s="155" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="156"/>
-      <c r="E25" s="156"/>
-      <c r="F25" s="157"/>
-    </row>
-    <row r="26" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="29"/>
-      <c r="B26" s="30">
-        <v>5</v>
-      </c>
-      <c r="C26" s="155" t="s">
-        <v>103</v>
-      </c>
-      <c r="D26" s="156"/>
-      <c r="E26" s="156"/>
-      <c r="F26" s="157"/>
-    </row>
-    <row r="27" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="28"/>
-      <c r="B27" s="27">
-        <v>6</v>
-      </c>
-      <c r="C27" s="195" t="s">
-        <v>97</v>
-      </c>
-      <c r="D27" s="196"/>
-      <c r="E27" s="196"/>
-      <c r="F27" s="197"/>
-    </row>
-    <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="23">
-        <v>1</v>
-      </c>
-      <c r="C28" s="109"/>
-      <c r="D28" s="110"/>
-      <c r="E28" s="110"/>
-      <c r="F28" s="111"/>
-    </row>
-    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="31"/>
-      <c r="B29" s="25">
-        <v>2</v>
-      </c>
-      <c r="C29" s="158"/>
-      <c r="D29" s="159"/>
-      <c r="E29" s="159"/>
-      <c r="F29" s="160"/>
-    </row>
-    <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="31"/>
-      <c r="B30" s="25">
-        <v>3</v>
-      </c>
-      <c r="C30" s="120" t="s">
-        <v>104</v>
-      </c>
-      <c r="D30" s="121"/>
-      <c r="E30" s="121"/>
-      <c r="F30" s="122"/>
-    </row>
-    <row r="31" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="31"/>
-      <c r="B31" s="25">
-        <v>4</v>
-      </c>
-      <c r="C31" s="102" t="s">
+      <c r="D36" s="215"/>
+      <c r="E36" s="215"/>
+      <c r="F36" s="216"/>
+      <c r="G36" s="91" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="83"/>
-      <c r="E31" s="83"/>
-      <c r="F31" s="84"/>
-    </row>
-    <row r="32" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="32"/>
-      <c r="B32" s="27">
-        <v>5</v>
-      </c>
-      <c r="C32" s="192"/>
-      <c r="D32" s="193"/>
-      <c r="E32" s="193"/>
-      <c r="F32" s="194"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="B33" s="23">
-        <v>2</v>
-      </c>
-      <c r="C33" s="189" t="s">
-        <v>30</v>
-      </c>
-      <c r="D33" s="190"/>
-      <c r="E33" s="190"/>
-      <c r="F33" s="191"/>
-    </row>
-    <row r="34" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="47"/>
-      <c r="B34" s="27">
-        <v>3</v>
-      </c>
-      <c r="C34" s="180"/>
-      <c r="D34" s="181"/>
-      <c r="E34" s="181"/>
-      <c r="F34" s="182"/>
-    </row>
-    <row r="35" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="48"/>
-      <c r="B35" s="49"/>
-      <c r="C35" s="183"/>
-      <c r="D35" s="184"/>
-      <c r="E35" s="184"/>
-      <c r="F35" s="185"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="39"/>
-      <c r="B36" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" s="186" t="s">
-        <v>35</v>
-      </c>
-      <c r="D36" s="187"/>
-      <c r="E36" s="187"/>
-      <c r="F36" s="188"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="50"/>
-      <c r="B37" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C37" s="136" t="s">
-        <v>36</v>
-      </c>
-      <c r="D37" s="137"/>
-      <c r="E37" s="137"/>
-      <c r="F37" s="138"/>
-    </row>
-    <row r="38" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="41"/>
-      <c r="B38" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="177" t="s">
-        <v>80</v>
-      </c>
-      <c r="D38" s="178"/>
-      <c r="E38" s="178"/>
-      <c r="F38" s="179"/>
-    </row>
-    <row r="39" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="70" t="s">
-        <v>54</v>
-      </c>
-      <c r="B39" s="71"/>
-      <c r="C39" s="167" t="s">
-        <v>93</v>
-      </c>
-      <c r="D39" s="167"/>
-      <c r="E39" s="167"/>
-      <c r="F39" s="167"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="54"/>
+      <c r="B37" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="122" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" s="123"/>
+      <c r="E37" s="123"/>
+      <c r="F37" s="124"/>
+      <c r="G37" s="89" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="42"/>
+      <c r="B38" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="205" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" s="206"/>
+      <c r="E38" s="206"/>
+      <c r="F38" s="207"/>
+      <c r="G38" s="77" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="75" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" s="76"/>
+      <c r="C39" s="194" t="s">
+        <v>123</v>
+      </c>
+      <c r="D39" s="194"/>
+      <c r="E39" s="194"/>
+      <c r="F39" s="194"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B40" s="2" t="s">
         <v>16</v>
       </c>
@@ -3529,7 +3857,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B41" s="2" t="s">
         <v>17</v>
       </c>
@@ -3539,19 +3867,13 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C22:D22"/>
@@ -3568,13 +3890,19 @@
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C9">
     <cfRule type="expression" priority="1">
@@ -3597,7 +3925,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3606,10 +3934,11 @@
     <col min="4" max="4" width="18.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="21.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.42578125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -3617,15 +3946,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -3633,13 +3962,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -3649,29 +3978,29 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="52" t="s">
+    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="92" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="92"/>
+      <c r="C7" s="149" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="149"/>
       <c r="E7" s="10">
         <v>3</v>
       </c>
@@ -3679,37 +4008,37 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="84" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="14" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="233" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" s="233"/>
-      <c r="E9" s="233"/>
-      <c r="F9" s="233"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="43" t="s">
+    <row r="9" spans="1:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="44" t="s">
+      <c r="C9" s="253" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" s="253"/>
+      <c r="E9" s="253"/>
+      <c r="F9" s="253"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="45" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="18" t="s">
@@ -3718,318 +4047,380 @@
       <c r="D10" s="19"/>
       <c r="E10" s="20"/>
       <c r="F10" s="21"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="34">
+      <c r="G10" s="22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="35">
         <v>2</v>
       </c>
-      <c r="C11" s="109"/>
-      <c r="D11" s="110"/>
-      <c r="E11" s="110"/>
-      <c r="F11" s="111"/>
-    </row>
-    <row r="12" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25">
+      <c r="C11" s="164"/>
+      <c r="D11" s="165"/>
+      <c r="E11" s="165"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="64"/>
+    </row>
+    <row r="12" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26">
         <v>3</v>
       </c>
-      <c r="C12" s="237"/>
-      <c r="D12" s="129"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="130"/>
-    </row>
-    <row r="13" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25">
+      <c r="C12" s="257"/>
+      <c r="D12" s="115"/>
+      <c r="E12" s="115"/>
+      <c r="F12" s="116"/>
+      <c r="G12" s="85"/>
+    </row>
+    <row r="13" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26">
         <v>4</v>
       </c>
-      <c r="C13" s="245"/>
-      <c r="D13" s="246"/>
-      <c r="E13" s="246" t="s">
-        <v>106</v>
-      </c>
-      <c r="F13" s="247"/>
-    </row>
-    <row r="14" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27">
+      <c r="C13" s="238"/>
+      <c r="D13" s="239"/>
+      <c r="E13" s="239" t="s">
+        <v>141</v>
+      </c>
+      <c r="F13" s="240"/>
+      <c r="G13" s="85" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="27"/>
+      <c r="B14" s="28">
         <v>5</v>
       </c>
-      <c r="C14" s="163" t="s">
-        <v>107</v>
-      </c>
-      <c r="D14" s="164"/>
-      <c r="E14" s="164"/>
-      <c r="F14" s="241"/>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="23">
+      <c r="C14" s="230" t="s">
+        <v>142</v>
+      </c>
+      <c r="D14" s="231"/>
+      <c r="E14" s="231"/>
+      <c r="F14" s="234"/>
+      <c r="G14" s="98" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="24">
         <v>2</v>
       </c>
-      <c r="C15" s="222"/>
-      <c r="D15" s="223"/>
-      <c r="E15" s="223"/>
-      <c r="F15" s="224"/>
-    </row>
-    <row r="16" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="24"/>
-      <c r="B16" s="55">
+      <c r="C15" s="242"/>
+      <c r="D15" s="243"/>
+      <c r="E15" s="243"/>
+      <c r="F15" s="244"/>
+      <c r="G15" s="47"/>
+    </row>
+    <row r="16" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="25"/>
+      <c r="B16" s="59">
         <v>3</v>
       </c>
-      <c r="C16" s="225" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" s="226"/>
-      <c r="E16" s="226"/>
-      <c r="F16" s="173"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25">
+      <c r="C16" s="245" t="s">
+        <v>146</v>
+      </c>
+      <c r="D16" s="246"/>
+      <c r="E16" s="246"/>
+      <c r="F16" s="201"/>
+      <c r="G16" s="89" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="25"/>
+      <c r="B17" s="26">
         <v>4</v>
       </c>
-      <c r="C17" s="227" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="228"/>
-      <c r="E17" s="228"/>
-      <c r="F17" s="229"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="28"/>
-      <c r="B18" s="27">
+      <c r="C17" s="247" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="248"/>
+      <c r="E17" s="248"/>
+      <c r="F17" s="249"/>
+      <c r="G17" s="85" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="29"/>
+      <c r="B18" s="28">
         <v>5</v>
       </c>
-      <c r="C18" s="230" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="231"/>
-      <c r="E18" s="231"/>
-      <c r="F18" s="232"/>
-    </row>
-    <row r="19" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="23">
+      <c r="C18" s="250" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="251"/>
+      <c r="E18" s="251"/>
+      <c r="F18" s="252"/>
+      <c r="G18" s="77" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="24">
         <v>1</v>
       </c>
-      <c r="C19" s="242" t="s">
+      <c r="C19" s="235" t="s">
+        <v>143</v>
+      </c>
+      <c r="D19" s="236"/>
+      <c r="E19" s="236"/>
+      <c r="F19" s="237"/>
+      <c r="G19" s="85" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="25"/>
+      <c r="B20" s="26">
+        <v>2</v>
+      </c>
+      <c r="C20" s="178" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" s="241"/>
+      <c r="E20" s="241"/>
+      <c r="F20" s="181"/>
+      <c r="G20" s="85" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="25"/>
+      <c r="B21" s="26">
+        <v>3</v>
+      </c>
+      <c r="C21" s="159" t="s">
+        <v>155</v>
+      </c>
+      <c r="D21" s="160"/>
+      <c r="E21" s="160"/>
+      <c r="F21" s="170"/>
+      <c r="G21" s="85" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="29"/>
+      <c r="B22" s="28">
+        <v>4</v>
+      </c>
+      <c r="C22" s="109" t="s">
+        <v>155</v>
+      </c>
+      <c r="D22" s="110"/>
+      <c r="E22" s="110"/>
+      <c r="F22" s="111"/>
+      <c r="G22" s="93" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="24">
+        <v>2</v>
+      </c>
+      <c r="C23" s="254" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="255"/>
+      <c r="E23" s="255"/>
+      <c r="F23" s="256"/>
+      <c r="G23" s="85" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="25"/>
+      <c r="B24" s="26">
+        <v>3</v>
+      </c>
+      <c r="C24" s="247" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="248"/>
+      <c r="E24" s="248"/>
+      <c r="F24" s="249"/>
+      <c r="G24" s="85" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="25"/>
+      <c r="B25" s="26">
+        <v>5</v>
+      </c>
+      <c r="C25" s="159" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="160"/>
+      <c r="E25" s="160"/>
+      <c r="F25" s="170"/>
+      <c r="G25" s="85" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="29"/>
+      <c r="B26" s="28">
+        <v>6</v>
+      </c>
+      <c r="C26" s="161" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="162"/>
+      <c r="E26" s="162"/>
+      <c r="F26" s="190"/>
+      <c r="G26" s="85" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="270" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" s="271"/>
+      <c r="E27" s="271"/>
+      <c r="F27" s="272"/>
+      <c r="G27" s="64"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="32"/>
+      <c r="B28" s="26">
+        <v>5</v>
+      </c>
+      <c r="C28" s="159" t="s">
         <v>108</v>
       </c>
-      <c r="D19" s="243"/>
-      <c r="E19" s="243"/>
-      <c r="F19" s="244"/>
-    </row>
-    <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="24"/>
-      <c r="B20" s="25">
-        <v>2</v>
-      </c>
-      <c r="C20" s="85" t="s">
+      <c r="D28" s="160"/>
+      <c r="E28" s="160"/>
+      <c r="F28" s="170"/>
+      <c r="G28" s="85" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="32"/>
+      <c r="B29" s="26">
+        <v>6</v>
+      </c>
+      <c r="C29" s="273" t="s">
         <v>109</v>
       </c>
-      <c r="D20" s="248"/>
-      <c r="E20" s="248"/>
-      <c r="F20" s="88"/>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25">
-        <v>3</v>
-      </c>
-      <c r="C21" s="102" t="s">
-        <v>118</v>
-      </c>
-      <c r="D21" s="83"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="84"/>
-    </row>
-    <row r="22" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="28"/>
-      <c r="B22" s="27">
+      <c r="D29" s="274"/>
+      <c r="E29" s="274"/>
+      <c r="F29" s="275"/>
+      <c r="G29" s="85" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="33"/>
+      <c r="B30" s="28">
+        <v>7</v>
+      </c>
+      <c r="C30" s="267" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" s="268"/>
+      <c r="E30" s="268" t="s">
+        <v>63</v>
+      </c>
+      <c r="F30" s="269"/>
+      <c r="G30" s="93" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="24">
         <v>4</v>
       </c>
-      <c r="C22" s="123" t="s">
-        <v>118</v>
-      </c>
-      <c r="D22" s="124"/>
-      <c r="E22" s="124"/>
-      <c r="F22" s="125"/>
-    </row>
-    <row r="23" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="23">
-        <v>2</v>
-      </c>
-      <c r="C23" s="234" t="s">
+      <c r="C31" s="214" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="215"/>
+      <c r="E31" s="215"/>
+      <c r="F31" s="216"/>
+      <c r="G31" s="64"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="41"/>
+      <c r="B32" s="26">
+        <v>5</v>
+      </c>
+      <c r="C32" s="258"/>
+      <c r="D32" s="259"/>
+      <c r="E32" s="259"/>
+      <c r="F32" s="260"/>
+      <c r="G32" s="83"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="50"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="208"/>
+      <c r="D33" s="209"/>
+      <c r="E33" s="209"/>
+      <c r="F33" s="210"/>
+      <c r="G33" s="81"/>
+    </row>
+    <row r="34" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="51"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="261"/>
+      <c r="D34" s="262"/>
+      <c r="E34" s="262"/>
+      <c r="F34" s="263"/>
+      <c r="G34" s="82"/>
+    </row>
+    <row r="35" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="57"/>
+      <c r="B35" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="264" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="235"/>
-      <c r="E23" s="235"/>
-      <c r="F23" s="236"/>
-    </row>
-    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25">
-        <v>3</v>
-      </c>
-      <c r="C24" s="227" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" s="228"/>
-      <c r="E24" s="228"/>
-      <c r="F24" s="229"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25">
-        <v>5</v>
-      </c>
-      <c r="C25" s="102" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="84"/>
-    </row>
-    <row r="26" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="28"/>
-      <c r="B26" s="27">
-        <v>6</v>
-      </c>
-      <c r="C26" s="103" t="s">
-        <v>42</v>
-      </c>
-      <c r="D26" s="104"/>
-      <c r="E26" s="104"/>
-      <c r="F26" s="206"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27" s="216" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" s="217"/>
-      <c r="E27" s="217"/>
-      <c r="F27" s="218"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="31"/>
-      <c r="B28" s="25">
-        <v>5</v>
-      </c>
-      <c r="C28" s="102" t="s">
-        <v>82</v>
-      </c>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="84"/>
-    </row>
-    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="31"/>
-      <c r="B29" s="25">
-        <v>6</v>
-      </c>
-      <c r="C29" s="219" t="s">
-        <v>83</v>
-      </c>
-      <c r="D29" s="220"/>
-      <c r="E29" s="220"/>
-      <c r="F29" s="221"/>
-    </row>
-    <row r="30" spans="1:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="32"/>
-      <c r="B30" s="27">
-        <v>7</v>
-      </c>
-      <c r="C30" s="213" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="214"/>
-      <c r="E30" s="214" t="s">
+      <c r="D35" s="265"/>
+      <c r="E35" s="265"/>
+      <c r="F35" s="266"/>
+      <c r="G35" s="95" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="215"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" s="23">
-        <v>4</v>
-      </c>
-      <c r="C31" s="186" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" s="187"/>
-      <c r="E31" s="187"/>
-      <c r="F31" s="188"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="40"/>
-      <c r="B32" s="25">
-        <v>5</v>
-      </c>
-      <c r="C32" s="238"/>
-      <c r="D32" s="239"/>
-      <c r="E32" s="239"/>
-      <c r="F32" s="240"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="47"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="180"/>
-      <c r="D33" s="181"/>
-      <c r="E33" s="181"/>
-      <c r="F33" s="182"/>
-    </row>
-    <row r="34" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="48"/>
-      <c r="B34" s="49"/>
-      <c r="C34" s="207"/>
-      <c r="D34" s="208"/>
-      <c r="E34" s="208"/>
-      <c r="F34" s="209"/>
-    </row>
-    <row r="35" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="53"/>
-      <c r="B35" s="73" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="210" t="s">
-        <v>40</v>
-      </c>
-      <c r="D35" s="211"/>
-      <c r="E35" s="211"/>
-      <c r="F35" s="212"/>
-    </row>
-    <row r="36" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="70" t="s">
-        <v>54</v>
-      </c>
-      <c r="B36" s="71"/>
-      <c r="C36" s="167" t="s">
-        <v>55</v>
-      </c>
-      <c r="D36" s="167"/>
-      <c r="E36" s="167"/>
-      <c r="F36" s="167"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="36" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="75" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="76"/>
+      <c r="C36" s="194" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" s="194"/>
+      <c r="E36" s="194"/>
+      <c r="F36" s="194"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
@@ -4037,7 +4428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B38" s="2" t="s">
         <v>17</v>
       </c>
@@ -4047,11 +4438,16 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C31:F31"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C15:F15"/>
@@ -4068,16 +4464,11 @@
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C20:F20"/>
   </mergeCells>
   <conditionalFormatting sqref="C9">
     <cfRule type="expression" priority="1">
@@ -4100,7 +4491,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -4109,10 +4500,11 @@
     <col min="4" max="4" width="20.42578125" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="20.140625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -4120,15 +4512,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -4136,13 +4528,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -4152,29 +4544,29 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="52" t="s">
+    <row r="7" spans="1:9" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="92" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="92"/>
+      <c r="C7" s="149" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="149"/>
       <c r="E7" s="10">
         <v>4</v>
       </c>
@@ -4182,37 +4574,37 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="84" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="14" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="233" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="233"/>
-      <c r="E9" s="233"/>
-      <c r="F9" s="233"/>
-    </row>
-    <row r="10" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="43" t="s">
+    <row r="9" spans="1:9" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="44" t="s">
+      <c r="C9" s="253" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="253"/>
+      <c r="E9" s="253"/>
+      <c r="F9" s="253"/>
+    </row>
+    <row r="10" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="45" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="18" t="s">
@@ -4221,431 +4613,516 @@
       <c r="D10" s="19"/>
       <c r="E10" s="20"/>
       <c r="F10" s="21"/>
-    </row>
-    <row r="11" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="34">
+      <c r="G10" s="96" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="35">
         <v>2</v>
       </c>
-      <c r="C11" s="275" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="276"/>
-      <c r="E11" s="276"/>
-      <c r="F11" s="277"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-    </row>
-    <row r="12" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25">
+      <c r="C11" s="307" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" s="308"/>
+      <c r="E11" s="308"/>
+      <c r="F11" s="309"/>
+      <c r="G11" s="90" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="63"/>
+      <c r="I11" s="63"/>
+    </row>
+    <row r="12" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26">
         <v>3</v>
       </c>
-      <c r="C12" s="262" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="263"/>
-      <c r="E12" s="263"/>
-      <c r="F12" s="264"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-    </row>
-    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25">
+      <c r="C12" s="310" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="311"/>
+      <c r="E12" s="311"/>
+      <c r="F12" s="312"/>
+      <c r="G12" s="85" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63"/>
+    </row>
+    <row r="13" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26">
         <v>4</v>
       </c>
-      <c r="C13" s="255" t="s">
-        <v>116</v>
-      </c>
-      <c r="D13" s="256"/>
-      <c r="E13" s="256"/>
-      <c r="F13" s="257"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="59"/>
-    </row>
-    <row r="14" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="24"/>
-      <c r="B14" s="25">
+      <c r="C13" s="319" t="s">
+        <v>153</v>
+      </c>
+      <c r="D13" s="320"/>
+      <c r="E13" s="320"/>
+      <c r="F13" s="321"/>
+      <c r="G13" s="85" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+    </row>
+    <row r="14" spans="1:9" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="25"/>
+      <c r="B14" s="26">
         <v>5</v>
       </c>
-      <c r="C14" s="249" t="s">
-        <v>117</v>
-      </c>
-      <c r="D14" s="250"/>
-      <c r="E14" s="250"/>
-      <c r="F14" s="251"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="59"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A15" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="23">
+      <c r="C14" s="295" t="s">
+        <v>154</v>
+      </c>
+      <c r="D14" s="281"/>
+      <c r="E14" s="281"/>
+      <c r="F14" s="282"/>
+      <c r="G14" s="85" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" s="63"/>
+      <c r="I14" s="63"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A15" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="24">
         <v>3</v>
       </c>
-      <c r="C15" s="272" t="s">
-        <v>113</v>
-      </c>
-      <c r="D15" s="273"/>
-      <c r="E15" s="273"/>
-      <c r="F15" s="274"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="59"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25">
+      <c r="C15" s="304" t="s">
+        <v>150</v>
+      </c>
+      <c r="D15" s="305"/>
+      <c r="E15" s="305"/>
+      <c r="F15" s="306"/>
+      <c r="G15" s="91" t="s">
+        <v>87</v>
+      </c>
+      <c r="H15" s="63"/>
+      <c r="I15" s="63"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26">
         <v>4</v>
       </c>
       <c r="C16" s="286" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="D16" s="287"/>
       <c r="E16" s="287"/>
       <c r="F16" s="288"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="59"/>
-    </row>
-    <row r="17" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25">
+      <c r="G16" s="89" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="63"/>
+      <c r="I16" s="63"/>
+    </row>
+    <row r="17" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="25"/>
+      <c r="B17" s="26">
         <v>5</v>
       </c>
       <c r="C17" s="286" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="D17" s="287"/>
       <c r="E17" s="287" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F17" s="288"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="59"/>
-    </row>
-    <row r="18" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="24"/>
-      <c r="B18" s="25">
+      <c r="G17" s="89" t="s">
+        <v>148</v>
+      </c>
+      <c r="H17" s="63"/>
+      <c r="I17" s="63"/>
+    </row>
+    <row r="18" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="25"/>
+      <c r="B18" s="26">
         <v>6</v>
       </c>
-      <c r="C18" s="249" t="s">
-        <v>115</v>
-      </c>
-      <c r="D18" s="250"/>
-      <c r="E18" s="250" t="s">
-        <v>112</v>
-      </c>
-      <c r="F18" s="295"/>
-      <c r="G18" s="59"/>
-      <c r="H18" s="59"/>
-    </row>
-    <row r="19" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="28"/>
-      <c r="B19" s="27">
+      <c r="C18" s="295" t="s">
+        <v>152</v>
+      </c>
+      <c r="D18" s="281"/>
+      <c r="E18" s="281" t="s">
+        <v>149</v>
+      </c>
+      <c r="F18" s="296"/>
+      <c r="G18" s="89" t="s">
+        <v>148</v>
+      </c>
+      <c r="H18" s="63"/>
+      <c r="I18" s="63"/>
+    </row>
+    <row r="19" spans="1:9" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="29"/>
+      <c r="B19" s="28">
         <v>7</v>
       </c>
-      <c r="C19" s="296"/>
-      <c r="D19" s="297"/>
-      <c r="E19" s="298" t="s">
-        <v>112</v>
-      </c>
-      <c r="F19" s="299"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="59"/>
-    </row>
-    <row r="20" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="23">
+      <c r="C19" s="297"/>
+      <c r="D19" s="298"/>
+      <c r="E19" s="299" t="s">
+        <v>149</v>
+      </c>
+      <c r="F19" s="300"/>
+      <c r="G19" s="77" t="s">
+        <v>94</v>
+      </c>
+      <c r="H19" s="63"/>
+      <c r="I19" s="63"/>
+    </row>
+    <row r="20" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="24">
         <v>2</v>
       </c>
-      <c r="C20" s="265" t="s">
-        <v>119</v>
-      </c>
-      <c r="D20" s="266"/>
-      <c r="E20" s="266"/>
-      <c r="F20" s="267"/>
-      <c r="G20" s="59"/>
-      <c r="H20" s="59"/>
-    </row>
-    <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25">
+      <c r="C20" s="326" t="s">
+        <v>156</v>
+      </c>
+      <c r="D20" s="327"/>
+      <c r="E20" s="327"/>
+      <c r="F20" s="328"/>
+      <c r="G20" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="H20" s="63"/>
+      <c r="I20" s="63"/>
+    </row>
+    <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="25"/>
+      <c r="B21" s="26">
         <v>3</v>
       </c>
-      <c r="C21" s="249" t="s">
-        <v>120</v>
-      </c>
-      <c r="D21" s="250"/>
-      <c r="E21" s="250"/>
-      <c r="F21" s="251"/>
-      <c r="G21" s="59"/>
-      <c r="H21" s="59"/>
-    </row>
-    <row r="22" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="29"/>
-      <c r="B22" s="30">
+      <c r="C21" s="295" t="s">
+        <v>157</v>
+      </c>
+      <c r="D21" s="281"/>
+      <c r="E21" s="281"/>
+      <c r="F21" s="282"/>
+      <c r="G21" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="H21" s="63"/>
+      <c r="I21" s="63"/>
+    </row>
+    <row r="22" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="30"/>
+      <c r="B22" s="31">
         <v>4</v>
       </c>
-      <c r="C22" s="249" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" s="250"/>
-      <c r="E22" s="250"/>
-      <c r="F22" s="251"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="59"/>
-    </row>
-    <row r="23" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="29"/>
-      <c r="B23" s="30">
+      <c r="C22" s="295" t="s">
+        <v>158</v>
+      </c>
+      <c r="D22" s="281"/>
+      <c r="E22" s="281"/>
+      <c r="F22" s="282"/>
+      <c r="G22" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="63"/>
+      <c r="I22" s="63"/>
+    </row>
+    <row r="23" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="30"/>
+      <c r="B23" s="31">
         <v>5</v>
       </c>
-      <c r="C23" s="258"/>
-      <c r="D23" s="259"/>
-      <c r="E23" s="250" t="s">
-        <v>122</v>
-      </c>
-      <c r="F23" s="251"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-    </row>
-    <row r="24" spans="1:8" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="28"/>
-      <c r="B24" s="27">
+      <c r="C23" s="322"/>
+      <c r="D23" s="323"/>
+      <c r="E23" s="281" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23" s="282"/>
+      <c r="G23" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="H23" s="63"/>
+      <c r="I23" s="63"/>
+    </row>
+    <row r="24" spans="1:9" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="29"/>
+      <c r="B24" s="28">
         <v>6</v>
       </c>
-      <c r="C24" s="260"/>
-      <c r="D24" s="261"/>
-      <c r="E24" s="253" t="s">
-        <v>122</v>
-      </c>
-      <c r="F24" s="254"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A25" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="34">
+      <c r="C24" s="324"/>
+      <c r="D24" s="325"/>
+      <c r="E24" s="313" t="s">
+        <v>159</v>
+      </c>
+      <c r="F24" s="314"/>
+      <c r="G24" s="93" t="s">
+        <v>110</v>
+      </c>
+      <c r="H24" s="63"/>
+      <c r="I24" s="63"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A25" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="35">
         <v>1</v>
       </c>
       <c r="C25" s="289" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="D25" s="290"/>
       <c r="E25" s="290"/>
       <c r="F25" s="291"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A26" s="24"/>
-      <c r="B26" s="25">
+      <c r="G25" s="85" t="s">
+        <v>89</v>
+      </c>
+      <c r="H25" s="63"/>
+      <c r="I25" s="63"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A26" s="25"/>
+      <c r="B26" s="26">
         <v>2</v>
       </c>
       <c r="C26" s="292" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="D26" s="293"/>
       <c r="E26" s="293"/>
       <c r="F26" s="294"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="59"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A27" s="24"/>
-      <c r="B27" s="25">
+      <c r="G26" s="85" t="s">
+        <v>89</v>
+      </c>
+      <c r="H26" s="63"/>
+      <c r="I26" s="63"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A27" s="25"/>
+      <c r="B27" s="26">
         <v>4</v>
       </c>
       <c r="C27" s="283" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="D27" s="284"/>
       <c r="E27" s="284"/>
       <c r="F27" s="285"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="59"/>
-    </row>
-    <row r="28" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="28"/>
-      <c r="B28" s="27">
+      <c r="G27" s="85" t="s">
+        <v>41</v>
+      </c>
+      <c r="H27" s="63"/>
+      <c r="I27" s="63"/>
+    </row>
+    <row r="28" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="29"/>
+      <c r="B28" s="28">
         <v>5</v>
       </c>
-      <c r="C28" s="278" t="s">
-        <v>124</v>
-      </c>
-      <c r="D28" s="279"/>
-      <c r="E28" s="279"/>
-      <c r="F28" s="280"/>
-      <c r="G28" s="59"/>
-      <c r="H28" s="59"/>
-    </row>
-    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="23">
+      <c r="C28" s="276" t="s">
+        <v>161</v>
+      </c>
+      <c r="D28" s="277"/>
+      <c r="E28" s="277"/>
+      <c r="F28" s="278"/>
+      <c r="G28" s="85" t="s">
+        <v>41</v>
+      </c>
+      <c r="H28" s="63"/>
+      <c r="I28" s="63"/>
+    </row>
+    <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="24">
         <v>3</v>
       </c>
-      <c r="C29" s="269"/>
-      <c r="D29" s="270"/>
-      <c r="E29" s="270"/>
-      <c r="F29" s="271"/>
-      <c r="G29" s="59"/>
-      <c r="H29" s="59"/>
-    </row>
-    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="31"/>
-      <c r="B30" s="25">
+      <c r="C29" s="315"/>
+      <c r="D29" s="316"/>
+      <c r="E29" s="316"/>
+      <c r="F29" s="317"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="63"/>
+    </row>
+    <row r="30" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="32"/>
+      <c r="B30" s="26">
         <v>4</v>
       </c>
-      <c r="C30" s="262" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="263"/>
-      <c r="E30" s="263" t="s">
-        <v>68</v>
-      </c>
-      <c r="F30" s="264"/>
-      <c r="G30" s="59"/>
-      <c r="H30" s="59"/>
-    </row>
-    <row r="31" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="31"/>
-      <c r="B31" s="25">
+      <c r="C30" s="310" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" s="311"/>
+      <c r="E30" s="311" t="s">
+        <v>91</v>
+      </c>
+      <c r="F30" s="312"/>
+      <c r="G30" s="85" t="s">
+        <v>78</v>
+      </c>
+      <c r="H30" s="63"/>
+      <c r="I30" s="63"/>
+    </row>
+    <row r="31" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="32"/>
+      <c r="B31" s="26">
         <v>5</v>
       </c>
-      <c r="C31" s="249" t="s">
-        <v>125</v>
-      </c>
-      <c r="D31" s="250"/>
-      <c r="E31" s="259"/>
-      <c r="F31" s="268"/>
-      <c r="G31" s="59"/>
-      <c r="H31" s="59"/>
-    </row>
-    <row r="32" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="31"/>
-      <c r="B32" s="25">
+      <c r="C31" s="295" t="s">
+        <v>162</v>
+      </c>
+      <c r="D31" s="281"/>
+      <c r="E31" s="323"/>
+      <c r="F31" s="329"/>
+      <c r="G31" s="85" t="s">
+        <v>94</v>
+      </c>
+      <c r="H31" s="63"/>
+      <c r="I31" s="63"/>
+    </row>
+    <row r="32" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="32"/>
+      <c r="B32" s="26">
         <v>6</v>
       </c>
-      <c r="C32" s="249" t="s">
-        <v>125</v>
-      </c>
-      <c r="D32" s="250"/>
-      <c r="E32" s="250" t="s">
-        <v>65</v>
-      </c>
-      <c r="F32" s="251"/>
-      <c r="G32" s="59"/>
-      <c r="H32" s="59"/>
-    </row>
-    <row r="33" spans="1:8" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="32"/>
-      <c r="B33" s="27">
+      <c r="C32" s="295" t="s">
+        <v>162</v>
+      </c>
+      <c r="D32" s="281"/>
+      <c r="E32" s="281" t="s">
+        <v>86</v>
+      </c>
+      <c r="F32" s="282"/>
+      <c r="G32" s="85" t="s">
+        <v>190</v>
+      </c>
+      <c r="H32" s="63"/>
+      <c r="I32" s="63"/>
+    </row>
+    <row r="33" spans="1:9" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="33"/>
+      <c r="B33" s="28">
         <v>7</v>
       </c>
-      <c r="C33" s="252" t="s">
-        <v>125</v>
-      </c>
-      <c r="D33" s="253"/>
-      <c r="E33" s="253" t="s">
-        <v>126</v>
-      </c>
-      <c r="F33" s="254"/>
-      <c r="G33" s="59"/>
-      <c r="H33" s="59"/>
-    </row>
-    <row r="34" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="B34" s="23">
+      <c r="C33" s="318" t="s">
+        <v>162</v>
+      </c>
+      <c r="D33" s="313"/>
+      <c r="E33" s="313" t="s">
+        <v>163</v>
+      </c>
+      <c r="F33" s="314"/>
+      <c r="G33" s="92" t="s">
+        <v>190</v>
+      </c>
+      <c r="H33" s="63"/>
+      <c r="I33" s="63"/>
+    </row>
+    <row r="34" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="24">
         <v>1</v>
       </c>
-      <c r="C34" s="300" t="s">
-        <v>64</v>
-      </c>
-      <c r="D34" s="301"/>
-      <c r="E34" s="301"/>
-      <c r="F34" s="302"/>
-      <c r="G34" s="59"/>
-      <c r="H34" s="59"/>
-    </row>
-    <row r="35" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="40"/>
-      <c r="B35" s="25">
+      <c r="C34" s="301" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" s="302"/>
+      <c r="E34" s="302"/>
+      <c r="F34" s="303"/>
+      <c r="G34" s="99" t="s">
+        <v>189</v>
+      </c>
+      <c r="H34" s="63"/>
+      <c r="I34" s="63"/>
+    </row>
+    <row r="35" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="41"/>
+      <c r="B35" s="26">
         <v>2</v>
       </c>
-      <c r="C35" s="249" t="s">
-        <v>63</v>
-      </c>
-      <c r="D35" s="250"/>
-      <c r="E35" s="250"/>
-      <c r="F35" s="251"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="59"/>
-    </row>
-    <row r="36" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="40"/>
-      <c r="B36" s="25">
+      <c r="C35" s="295" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" s="281"/>
+      <c r="E35" s="281"/>
+      <c r="F35" s="282"/>
+      <c r="G35" s="85" t="s">
+        <v>189</v>
+      </c>
+      <c r="H35" s="63"/>
+      <c r="I35" s="63"/>
+    </row>
+    <row r="36" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="41"/>
+      <c r="B36" s="26">
         <v>3</v>
       </c>
-      <c r="C36" s="281"/>
-      <c r="D36" s="282"/>
-      <c r="E36" s="250" t="s">
-        <v>127</v>
-      </c>
-      <c r="F36" s="251"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="59"/>
-    </row>
-    <row r="37" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="36"/>
-      <c r="B37" s="30">
+      <c r="C36" s="279"/>
+      <c r="D36" s="280"/>
+      <c r="E36" s="281" t="s">
+        <v>164</v>
+      </c>
+      <c r="F36" s="282"/>
+      <c r="G36" s="85" t="s">
+        <v>79</v>
+      </c>
+      <c r="H36" s="63"/>
+      <c r="I36" s="63"/>
+    </row>
+    <row r="37" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="37"/>
+      <c r="B37" s="31">
         <v>4</v>
       </c>
-      <c r="C37" s="249" t="s">
-        <v>69</v>
-      </c>
-      <c r="D37" s="250"/>
-      <c r="E37" s="250"/>
-      <c r="F37" s="251"/>
-      <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-    </row>
-    <row r="38" spans="1:8" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="47"/>
-      <c r="B38" s="27">
+      <c r="C37" s="295" t="s">
+        <v>92</v>
+      </c>
+      <c r="D37" s="281"/>
+      <c r="E37" s="281"/>
+      <c r="F37" s="282"/>
+      <c r="G37" s="85" t="s">
+        <v>79</v>
+      </c>
+      <c r="H37" s="63"/>
+      <c r="I37" s="63"/>
+    </row>
+    <row r="38" spans="1:9" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="50"/>
+      <c r="B38" s="28">
         <v>5</v>
       </c>
-      <c r="C38" s="252" t="s">
-        <v>70</v>
-      </c>
-      <c r="D38" s="253"/>
-      <c r="E38" s="253"/>
-      <c r="F38" s="254"/>
-      <c r="G38" s="59"/>
-      <c r="H38" s="59"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="C38" s="318" t="s">
+        <v>93</v>
+      </c>
+      <c r="D38" s="313"/>
+      <c r="E38" s="313"/>
+      <c r="F38" s="314"/>
+      <c r="G38" s="98" t="s">
+        <v>79</v>
+      </c>
+      <c r="H38" s="63"/>
+      <c r="I38" s="63"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="59"/>
-      <c r="D39" s="59"/>
+      <c r="C39" s="63"/>
+      <c r="D39" s="63"/>
       <c r="E39" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F39" s="59"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="F39" s="63"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B40" s="2" t="s">
         <v>17</v>
       </c>
@@ -4655,6 +5132,32 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C12:F12"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="E36:F36"/>
@@ -4671,32 +5174,6 @@
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
   </mergeCells>
   <conditionalFormatting sqref="C9">
     <cfRule type="expression" priority="1">
@@ -4719,7 +5196,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -4728,10 +5205,11 @@
     <col min="4" max="4" width="21.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="22.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="21.140625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -4739,15 +5217,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -4755,13 +5233,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -4771,29 +5249,29 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="52" t="s">
+    <row r="7" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="92" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="92"/>
+      <c r="C7" s="149" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="149"/>
       <c r="E7" s="10">
         <v>5</v>
       </c>
@@ -4801,37 +5279,37 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="84" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="14" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="233" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" s="233"/>
-      <c r="E9" s="233"/>
-      <c r="F9" s="233"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="43" t="s">
+    <row r="9" spans="1:7" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="44" t="s">
+      <c r="C9" s="253" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="253"/>
+      <c r="E9" s="253"/>
+      <c r="F9" s="253"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="45" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="18" t="s">
@@ -4840,354 +5318,437 @@
       <c r="D10" s="19"/>
       <c r="E10" s="20"/>
       <c r="F10" s="21"/>
-    </row>
-    <row r="11" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="34">
+      <c r="G10" s="22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="35">
         <v>3</v>
       </c>
-      <c r="C11" s="200" t="s">
-        <v>133</v>
-      </c>
-      <c r="D11" s="201"/>
-      <c r="E11" s="201"/>
-      <c r="F11" s="202"/>
-    </row>
-    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25">
+      <c r="C11" s="184" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" s="185"/>
+      <c r="E11" s="185"/>
+      <c r="F11" s="186"/>
+      <c r="G11" s="101" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26">
         <v>4</v>
       </c>
-      <c r="C12" s="112" t="s">
-        <v>129</v>
-      </c>
-      <c r="D12" s="113"/>
-      <c r="E12" s="113"/>
-      <c r="F12" s="114"/>
-    </row>
-    <row r="13" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25">
+      <c r="C12" s="167" t="s">
+        <v>166</v>
+      </c>
+      <c r="D12" s="168"/>
+      <c r="E12" s="168"/>
+      <c r="F12" s="169"/>
+      <c r="G12" s="85" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26">
         <v>5</v>
       </c>
-      <c r="C13" s="112" t="s">
-        <v>130</v>
-      </c>
-      <c r="D13" s="113"/>
-      <c r="E13" s="113"/>
-      <c r="F13" s="114"/>
-    </row>
-    <row r="14" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="24"/>
-      <c r="B14" s="25">
+      <c r="C13" s="167" t="s">
+        <v>167</v>
+      </c>
+      <c r="D13" s="168"/>
+      <c r="E13" s="168"/>
+      <c r="F13" s="169"/>
+      <c r="G13" s="85" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="25"/>
+      <c r="B14" s="26">
         <v>6</v>
       </c>
-      <c r="C14" s="303" t="s">
-        <v>147</v>
-      </c>
-      <c r="D14" s="304"/>
-      <c r="E14" s="304"/>
-      <c r="F14" s="305"/>
-    </row>
-    <row r="15" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="26"/>
-      <c r="B15" s="57"/>
-      <c r="C15" s="306"/>
-      <c r="D15" s="165"/>
-      <c r="E15" s="165"/>
-      <c r="F15" s="166"/>
-    </row>
-    <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="23">
+      <c r="C14" s="340" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" s="341"/>
+      <c r="E14" s="341"/>
+      <c r="F14" s="342"/>
+      <c r="G14" s="85" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="27"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="343"/>
+      <c r="D15" s="232"/>
+      <c r="E15" s="232"/>
+      <c r="F15" s="233"/>
+      <c r="G15" s="81"/>
+    </row>
+    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="24">
         <v>1</v>
       </c>
-      <c r="C16" s="307" t="s">
+      <c r="C16" s="344" t="s">
+        <v>113</v>
+      </c>
+      <c r="D16" s="345"/>
+      <c r="E16" s="345"/>
+      <c r="F16" s="346"/>
+      <c r="G16" s="91" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="25"/>
+      <c r="B17" s="26">
+        <v>2</v>
+      </c>
+      <c r="C17" s="171" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" s="172"/>
+      <c r="E17" s="172"/>
+      <c r="F17" s="173"/>
+      <c r="G17" s="92" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="25"/>
+      <c r="B18" s="26">
+        <v>7</v>
+      </c>
+      <c r="C18" s="159" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="160"/>
+      <c r="E18" s="160"/>
+      <c r="F18" s="170"/>
+      <c r="G18" s="88" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="29"/>
+      <c r="B19" s="28">
+        <v>8</v>
+      </c>
+      <c r="C19" s="330" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="331"/>
+      <c r="E19" s="331"/>
+      <c r="F19" s="332"/>
+      <c r="G19" s="93" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="24">
+        <v>2</v>
+      </c>
+      <c r="C20" s="333"/>
+      <c r="D20" s="334"/>
+      <c r="E20" s="334"/>
+      <c r="F20" s="335"/>
+      <c r="G20" s="85"/>
+    </row>
+    <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="25"/>
+      <c r="B21" s="26">
+        <v>3</v>
+      </c>
+      <c r="C21" s="159" t="s">
+        <v>171</v>
+      </c>
+      <c r="D21" s="160"/>
+      <c r="E21" s="160"/>
+      <c r="F21" s="170"/>
+      <c r="G21" s="88" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="25"/>
+      <c r="B22" s="26">
+        <v>4</v>
+      </c>
+      <c r="C22" s="159" t="s">
+        <v>172</v>
+      </c>
+      <c r="D22" s="160"/>
+      <c r="E22" s="160"/>
+      <c r="F22" s="170"/>
+      <c r="G22" s="88" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="30"/>
+      <c r="B23" s="31">
+        <v>5</v>
+      </c>
+      <c r="C23" s="347" t="s">
+        <v>191</v>
+      </c>
+      <c r="D23" s="348"/>
+      <c r="E23" s="348"/>
+      <c r="F23" s="349"/>
+      <c r="G23" s="93" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="24">
+        <v>2</v>
+      </c>
+      <c r="C24" s="176" t="s">
+        <v>185</v>
+      </c>
+      <c r="D24" s="176"/>
+      <c r="E24" s="176" t="s">
+        <v>186</v>
+      </c>
+      <c r="F24" s="177"/>
+      <c r="G24" s="90" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="25"/>
+      <c r="B25" s="26">
+        <v>3</v>
+      </c>
+      <c r="C25" s="160" t="s">
+        <v>188</v>
+      </c>
+      <c r="D25" s="160"/>
+      <c r="E25" s="160"/>
+      <c r="F25" s="170"/>
+      <c r="G25" s="85" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="30"/>
+      <c r="B26" s="31">
+        <v>4</v>
+      </c>
+      <c r="C26" s="160" t="s">
+        <v>192</v>
+      </c>
+      <c r="D26" s="160"/>
+      <c r="E26" s="160"/>
+      <c r="F26" s="170"/>
+      <c r="G26" s="97" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="56.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="30"/>
+      <c r="B27" s="31">
+        <v>5</v>
+      </c>
+      <c r="C27" s="160" t="s">
+        <v>193</v>
+      </c>
+      <c r="D27" s="160"/>
+      <c r="E27" s="160"/>
+      <c r="F27" s="170"/>
+      <c r="G27" s="97" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="30"/>
+      <c r="B28" s="31">
+        <v>6</v>
+      </c>
+      <c r="C28" s="115"/>
+      <c r="D28" s="115"/>
+      <c r="E28" s="160" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="308"/>
-      <c r="E16" s="308"/>
-      <c r="F16" s="309"/>
-    </row>
-    <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25">
+      <c r="F28" s="170"/>
+      <c r="G28" s="97" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="30"/>
+      <c r="B29" s="31">
+        <v>7</v>
+      </c>
+      <c r="C29" s="115"/>
+      <c r="D29" s="115"/>
+      <c r="E29" s="160" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29" s="170"/>
+      <c r="G29" s="97" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="29"/>
+      <c r="B30" s="28">
+        <v>8</v>
+      </c>
+      <c r="C30" s="350"/>
+      <c r="D30" s="350"/>
+      <c r="E30" s="337" t="s">
+        <v>86</v>
+      </c>
+      <c r="F30" s="338"/>
+      <c r="G30" s="97" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="35">
         <v>2</v>
       </c>
-      <c r="C17" s="115" t="s">
-        <v>87</v>
-      </c>
-      <c r="D17" s="116"/>
-      <c r="E17" s="116"/>
-      <c r="F17" s="117"/>
-    </row>
-    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="24"/>
-      <c r="B18" s="25">
-        <v>7</v>
-      </c>
-      <c r="C18" s="102" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="83"/>
-      <c r="E18" s="83"/>
-      <c r="F18" s="84"/>
-    </row>
-    <row r="19" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="28"/>
-      <c r="B19" s="27">
-        <v>8</v>
-      </c>
-      <c r="C19" s="314" t="s">
+      <c r="C31" s="217" t="s">
+        <v>168</v>
+      </c>
+      <c r="D31" s="218"/>
+      <c r="E31" s="218"/>
+      <c r="F31" s="219"/>
+      <c r="G31" s="90" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="32"/>
+      <c r="B32" s="26">
+        <v>3</v>
+      </c>
+      <c r="C32" s="171" t="s">
+        <v>169</v>
+      </c>
+      <c r="D32" s="172"/>
+      <c r="E32" s="172"/>
+      <c r="F32" s="173"/>
+      <c r="G32" s="85" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="32"/>
+      <c r="B33" s="26">
+        <v>4</v>
+      </c>
+      <c r="C33" s="171" t="s">
+        <v>115</v>
+      </c>
+      <c r="D33" s="172"/>
+      <c r="E33" s="172"/>
+      <c r="F33" s="173"/>
+      <c r="G33" s="85" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="33"/>
+      <c r="B34" s="28">
+        <v>5</v>
+      </c>
+      <c r="C34" s="161" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" s="162"/>
+      <c r="E34" s="162"/>
+      <c r="F34" s="190"/>
+      <c r="G34" s="85" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="24">
+        <v>2</v>
+      </c>
+      <c r="C35" s="339" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="315"/>
-      <c r="E19" s="315"/>
-      <c r="F19" s="316"/>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="23">
-        <v>2</v>
-      </c>
-      <c r="C20" s="321"/>
-      <c r="D20" s="322"/>
-      <c r="E20" s="322"/>
-      <c r="F20" s="323"/>
-    </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25">
+      <c r="D35" s="176"/>
+      <c r="E35" s="176" t="s">
+        <v>193</v>
+      </c>
+      <c r="F35" s="177"/>
+      <c r="G35" s="99" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="41"/>
+      <c r="B36" s="35">
         <v>3</v>
       </c>
-      <c r="C21" s="102" t="s">
-        <v>134</v>
-      </c>
-      <c r="D21" s="83"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="84"/>
-    </row>
-    <row r="22" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="24"/>
-      <c r="B22" s="25">
+      <c r="C36" s="159" t="s">
+        <v>84</v>
+      </c>
+      <c r="D36" s="160"/>
+      <c r="E36" s="135"/>
+      <c r="F36" s="136"/>
+      <c r="G36" s="97" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="41"/>
+      <c r="B37" s="35">
         <v>4</v>
       </c>
-      <c r="C22" s="102" t="s">
-        <v>135</v>
-      </c>
-      <c r="D22" s="83"/>
-      <c r="E22" s="83"/>
-      <c r="F22" s="84"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="29"/>
-      <c r="B23" s="30">
+      <c r="C37" s="159" t="s">
+        <v>84</v>
+      </c>
+      <c r="D37" s="160"/>
+      <c r="E37" s="135"/>
+      <c r="F37" s="136"/>
+      <c r="G37" s="97" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="50"/>
+      <c r="B38" s="28">
         <v>5</v>
       </c>
-      <c r="C23" s="317" t="s">
-        <v>152</v>
-      </c>
-      <c r="D23" s="318"/>
-      <c r="E23" s="318"/>
-      <c r="F23" s="319"/>
-    </row>
-    <row r="24" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="23">
-        <v>2</v>
-      </c>
-      <c r="C24" s="81" t="s">
-        <v>148</v>
-      </c>
-      <c r="D24" s="81"/>
-      <c r="E24" s="81" t="s">
-        <v>149</v>
-      </c>
-      <c r="F24" s="82"/>
-    </row>
-    <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25">
-        <v>3</v>
-      </c>
-      <c r="C25" s="83" t="s">
-        <v>151</v>
-      </c>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="84"/>
-    </row>
-    <row r="26" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="29"/>
-      <c r="B26" s="30">
-        <v>4</v>
-      </c>
-      <c r="C26" s="83" t="s">
-        <v>153</v>
-      </c>
-      <c r="D26" s="83"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="84"/>
-    </row>
-    <row r="27" spans="1:6" ht="56.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="29"/>
-      <c r="B27" s="30">
-        <v>5</v>
-      </c>
-      <c r="C27" s="83" t="s">
-        <v>154</v>
-      </c>
-      <c r="D27" s="83"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="84"/>
-    </row>
-    <row r="28" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="29"/>
-      <c r="B28" s="30">
-        <v>6</v>
-      </c>
-      <c r="C28" s="129"/>
-      <c r="D28" s="129"/>
-      <c r="E28" s="83" t="s">
-        <v>65</v>
-      </c>
-      <c r="F28" s="84"/>
-    </row>
-    <row r="29" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="29"/>
-      <c r="B29" s="30">
-        <v>7</v>
-      </c>
-      <c r="C29" s="129"/>
-      <c r="D29" s="129"/>
-      <c r="E29" s="83" t="s">
-        <v>65</v>
-      </c>
-      <c r="F29" s="84"/>
-    </row>
-    <row r="30" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="28"/>
-      <c r="B30" s="27">
-        <v>8</v>
-      </c>
-      <c r="C30" s="320"/>
-      <c r="D30" s="320"/>
-      <c r="E30" s="311" t="s">
-        <v>65</v>
-      </c>
-      <c r="F30" s="312"/>
-    </row>
-    <row r="31" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="34">
-        <v>2</v>
-      </c>
-      <c r="C31" s="189" t="s">
-        <v>131</v>
-      </c>
-      <c r="D31" s="190"/>
-      <c r="E31" s="190"/>
-      <c r="F31" s="191"/>
-    </row>
-    <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="31"/>
-      <c r="B32" s="25">
-        <v>3</v>
-      </c>
-      <c r="C32" s="115" t="s">
-        <v>132</v>
-      </c>
-      <c r="D32" s="116"/>
-      <c r="E32" s="116"/>
-      <c r="F32" s="117"/>
-    </row>
-    <row r="33" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="31"/>
-      <c r="B33" s="25">
-        <v>4</v>
-      </c>
-      <c r="C33" s="115" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" s="116"/>
-      <c r="E33" s="116"/>
-      <c r="F33" s="117"/>
-    </row>
-    <row r="34" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="32"/>
-      <c r="B34" s="27">
-        <v>5</v>
-      </c>
-      <c r="C34" s="103" t="s">
-        <v>150</v>
-      </c>
-      <c r="D34" s="104"/>
-      <c r="E34" s="104"/>
-      <c r="F34" s="206"/>
-    </row>
-    <row r="35" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="B35" s="23">
-        <v>2</v>
-      </c>
-      <c r="C35" s="313" t="s">
-        <v>63</v>
-      </c>
-      <c r="D35" s="81"/>
-      <c r="E35" s="81" t="s">
-        <v>154</v>
-      </c>
-      <c r="F35" s="82"/>
-    </row>
-    <row r="36" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="40"/>
-      <c r="B36" s="34">
-        <v>3</v>
-      </c>
-      <c r="C36" s="102" t="s">
-        <v>63</v>
-      </c>
-      <c r="D36" s="83"/>
-      <c r="E36" s="147"/>
-      <c r="F36" s="148"/>
-    </row>
-    <row r="37" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="40"/>
-      <c r="B37" s="34">
-        <v>4</v>
-      </c>
-      <c r="C37" s="102" t="s">
-        <v>63</v>
-      </c>
-      <c r="D37" s="83"/>
-      <c r="E37" s="147"/>
-      <c r="F37" s="148"/>
-    </row>
-    <row r="38" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="47"/>
-      <c r="B38" s="27">
-        <v>5</v>
-      </c>
-      <c r="C38" s="310" t="s">
-        <v>85</v>
-      </c>
-      <c r="D38" s="311"/>
-      <c r="E38" s="311"/>
-      <c r="F38" s="312"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C38" s="336" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38" s="337"/>
+      <c r="E38" s="337"/>
+      <c r="F38" s="338"/>
+      <c r="G38" s="98" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -5195,7 +5756,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B40" s="2" t="s">
         <v>17</v>
       </c>
@@ -5205,28 +5766,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E37:F37"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="E27:F27"/>
@@ -5240,9 +5779,31 @@
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C20:F20"/>
   </mergeCells>
   <conditionalFormatting sqref="C9">
     <cfRule type="expression" priority="1">
